--- a/research/traditional_assets/database/data/iceland/iceland_retail_general.xlsx
+++ b/research/traditional_assets/database/data/iceland/iceland_retail_general.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09643787407339022</v>
+        <v>0.09628099832524344</v>
       </c>
       <c r="C2">
-        <v>1039.039830251335</v>
+        <v>1031.035593632367</v>
       </c>
       <c r="D2">
-        <v>1017.339830251335</v>
+        <v>1019.866593632367</v>
       </c>
       <c r="E2">
-        <v>-221.7</v>
+        <v>-211.169</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>10.531</v>
       </c>
       <c r="G2">
         <v>21.7</v>
@@ -1451,28 +1451,28 @@
         <v>62.75</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.5297092999999999</v>
       </c>
       <c r="N2">
-        <v>62.75</v>
+        <v>62.2202907</v>
       </c>
       <c r="O2">
-        <v>12.55</v>
+        <v>12.44405814</v>
       </c>
       <c r="P2">
-        <v>50.2</v>
+        <v>49.77623256</v>
       </c>
       <c r="Q2">
-        <v>87.7</v>
+        <v>87.27623256</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09643787407339022</v>
+        <v>0.09684706901539741</v>
       </c>
       <c r="T2">
-        <v>0.9605817593200959</v>
+        <v>0.9683440361630866</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>118.4612012664305</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09628099832524344</v>
+        <v>0.09612412257709664</v>
       </c>
       <c r="C3">
-        <v>1031.035593632367</v>
+        <v>1023.043939691711</v>
       </c>
       <c r="D3">
-        <v>1019.866593632367</v>
+        <v>1022.405939691711</v>
       </c>
       <c r="E3">
-        <v>-211.169</v>
+        <v>-200.638</v>
       </c>
       <c r="F3">
-        <v>10.531</v>
+        <v>21.062</v>
       </c>
       <c r="G3">
         <v>21.7</v>
@@ -1533,28 +1533,28 @@
         <v>62.75</v>
       </c>
       <c r="M3">
-        <v>0.5297092999999999</v>
+        <v>1.0594186</v>
       </c>
       <c r="N3">
-        <v>62.2202907</v>
+        <v>61.6905814</v>
       </c>
       <c r="O3">
-        <v>12.44405814</v>
+        <v>12.33811628</v>
       </c>
       <c r="P3">
-        <v>49.77623256</v>
+        <v>49.35246512</v>
       </c>
       <c r="Q3">
-        <v>87.27623256</v>
+        <v>86.85246512000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09684706901539741</v>
+        <v>0.09726461487458841</v>
       </c>
       <c r="T3">
-        <v>0.9683440361630866</v>
+        <v>0.9762647268191995</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>118.4612012664305</v>
+        <v>59.23060063321525</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09612412257709664</v>
+        <v>0.09596724682894986</v>
       </c>
       <c r="C4">
-        <v>1023.043939691711</v>
+        <v>1015.064962652071</v>
       </c>
       <c r="D4">
-        <v>1022.405939691711</v>
+        <v>1024.957962652071</v>
       </c>
       <c r="E4">
-        <v>-200.638</v>
+        <v>-190.107</v>
       </c>
       <c r="F4">
-        <v>21.062</v>
+        <v>31.593</v>
       </c>
       <c r="G4">
         <v>21.7</v>
@@ -1615,28 +1615,28 @@
         <v>62.75</v>
       </c>
       <c r="M4">
-        <v>1.0594186</v>
+        <v>1.5891279</v>
       </c>
       <c r="N4">
-        <v>61.6905814</v>
+        <v>61.1608721</v>
       </c>
       <c r="O4">
-        <v>12.33811628</v>
+        <v>12.23217442</v>
       </c>
       <c r="P4">
-        <v>49.35246512</v>
+        <v>48.92869768</v>
       </c>
       <c r="Q4">
-        <v>86.85246512000001</v>
+        <v>86.42869768</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09726461487458841</v>
+        <v>0.09769076992675244</v>
       </c>
       <c r="T4">
-        <v>0.9762647268191995</v>
+        <v>0.9843487306847167</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>59.23060063321525</v>
+        <v>39.48706708881016</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09596724682894986</v>
+        <v>0.09581037108080309</v>
       </c>
       <c r="C5">
-        <v>1015.064962652071</v>
+        <v>1007.09875767926</v>
       </c>
       <c r="D5">
-        <v>1024.957962652071</v>
+        <v>1027.522757679259</v>
       </c>
       <c r="E5">
-        <v>-190.107</v>
+        <v>-179.576</v>
       </c>
       <c r="F5">
-        <v>31.593</v>
+        <v>42.124</v>
       </c>
       <c r="G5">
         <v>21.7</v>
@@ -1697,28 +1697,28 @@
         <v>62.75</v>
       </c>
       <c r="M5">
-        <v>1.5891279</v>
+        <v>2.1188372</v>
       </c>
       <c r="N5">
-        <v>61.1608721</v>
+        <v>60.6311628</v>
       </c>
       <c r="O5">
-        <v>12.23217442</v>
+        <v>12.12623256</v>
       </c>
       <c r="P5">
-        <v>48.92869768</v>
+        <v>48.50493024</v>
       </c>
       <c r="Q5">
-        <v>86.42869768</v>
+        <v>86.00493023999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09769076992675244</v>
+        <v>0.09812580320916989</v>
       </c>
       <c r="T5">
-        <v>0.9843487306847167</v>
+        <v>0.9926011512974325</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>39.48706708881016</v>
+        <v>29.61530031660762</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09581037108080309</v>
+        <v>0.0956534953326563</v>
       </c>
       <c r="C6">
-        <v>1007.09875767926</v>
+        <v>999.1454208940302</v>
       </c>
       <c r="D6">
-        <v>1027.522757679259</v>
+        <v>1030.10042089403</v>
       </c>
       <c r="E6">
-        <v>-179.576</v>
+        <v>-169.045</v>
       </c>
       <c r="F6">
-        <v>42.124</v>
+        <v>52.655</v>
       </c>
       <c r="G6">
         <v>21.7</v>
@@ -1779,28 +1779,28 @@
         <v>62.75</v>
       </c>
       <c r="M6">
-        <v>2.1188372</v>
+        <v>2.6485465</v>
       </c>
       <c r="N6">
-        <v>60.6311628</v>
+        <v>60.1014535</v>
       </c>
       <c r="O6">
-        <v>12.12623256</v>
+        <v>12.0202907</v>
       </c>
       <c r="P6">
-        <v>48.50493024</v>
+        <v>48.0811628</v>
       </c>
       <c r="Q6">
-        <v>86.00493023999999</v>
+        <v>85.5811628</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09812580320916989</v>
+        <v>0.09856999508700663</v>
       </c>
       <c r="T6">
-        <v>0.9926011512974325</v>
+        <v>1.001027307080942</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>29.61530031660762</v>
+        <v>23.69224025328609</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0956534953326563</v>
+        <v>0.09549661958450952</v>
       </c>
       <c r="C7">
-        <v>999.1454208940302</v>
+        <v>991.2050493840815</v>
       </c>
       <c r="D7">
-        <v>1030.10042089403</v>
+        <v>1032.691049384081</v>
       </c>
       <c r="E7">
-        <v>-169.045</v>
+        <v>-158.514</v>
       </c>
       <c r="F7">
-        <v>52.655</v>
+        <v>63.186</v>
       </c>
       <c r="G7">
         <v>21.7</v>
@@ -1861,28 +1861,28 @@
         <v>62.75</v>
       </c>
       <c r="M7">
-        <v>2.6485465</v>
+        <v>3.1782558</v>
       </c>
       <c r="N7">
-        <v>60.1014535</v>
+        <v>59.5717442</v>
       </c>
       <c r="O7">
-        <v>12.0202907</v>
+        <v>11.91434884</v>
       </c>
       <c r="P7">
-        <v>48.0811628</v>
+        <v>47.65739536</v>
       </c>
       <c r="Q7">
-        <v>85.5811628</v>
+        <v>85.15739536</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09856999508700663</v>
+        <v>0.0990236378558612</v>
       </c>
       <c r="T7">
-        <v>1.001027307080942</v>
+        <v>1.009632742774739</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>23.69224025328609</v>
+        <v>19.74353354440508</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09549661958450952</v>
+        <v>0.09533974383636276</v>
       </c>
       <c r="C8">
-        <v>991.2050493840815</v>
+        <v>983.2777412162496</v>
       </c>
       <c r="D8">
-        <v>1032.691049384081</v>
+        <v>1035.29474121625</v>
       </c>
       <c r="E8">
-        <v>-158.514</v>
+        <v>-147.983</v>
       </c>
       <c r="F8">
-        <v>63.18599999999999</v>
+        <v>73.71699999999998</v>
       </c>
       <c r="G8">
         <v>21.7</v>
@@ -1943,28 +1943,28 @@
         <v>62.75</v>
       </c>
       <c r="M8">
-        <v>3.1782558</v>
+        <v>3.707965099999999</v>
       </c>
       <c r="N8">
-        <v>59.5717442</v>
+        <v>59.0420349</v>
       </c>
       <c r="O8">
-        <v>11.91434884</v>
+        <v>11.80840698</v>
       </c>
       <c r="P8">
-        <v>47.65739536</v>
+        <v>47.23362792</v>
       </c>
       <c r="Q8">
-        <v>85.15739536</v>
+        <v>84.73362792</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0990236378558612</v>
+        <v>0.09948703638318576</v>
       </c>
       <c r="T8">
-        <v>1.009632742774739</v>
+        <v>1.018423241601736</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>19.74353354440508</v>
+        <v>16.92302875234721</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09533974383636275</v>
+        <v>0.09518286808821597</v>
       </c>
       <c r="C9">
-        <v>983.2777412162499</v>
+        <v>975.3635954488832</v>
       </c>
       <c r="D9">
-        <v>1035.29474121625</v>
+        <v>1037.911595448883</v>
       </c>
       <c r="E9">
-        <v>-147.983</v>
+        <v>-137.452</v>
       </c>
       <c r="F9">
-        <v>73.717</v>
+        <v>84.24799999999999</v>
       </c>
       <c r="G9">
         <v>21.7</v>
@@ -2025,28 +2025,28 @@
         <v>62.75</v>
       </c>
       <c r="M9">
-        <v>3.7079651</v>
+        <v>4.2376744</v>
       </c>
       <c r="N9">
-        <v>59.0420349</v>
+        <v>58.5123256</v>
       </c>
       <c r="O9">
-        <v>11.80840698</v>
+        <v>11.70246512</v>
       </c>
       <c r="P9">
-        <v>47.23362792</v>
+        <v>46.80986048</v>
       </c>
       <c r="Q9">
-        <v>84.73362792</v>
+        <v>84.30986048</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09948703638318576</v>
+        <v>0.09996050879153909</v>
       </c>
       <c r="T9">
-        <v>1.018423241601736</v>
+        <v>1.02740483822932</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>16.92302875234721</v>
+        <v>14.80765015830381</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09518286808821597</v>
+        <v>0.09502599234006918</v>
       </c>
       <c r="C10">
-        <v>975.3635954488832</v>
+        <v>967.462712144403</v>
       </c>
       <c r="D10">
-        <v>1037.911595448883</v>
+        <v>1040.541712144403</v>
       </c>
       <c r="E10">
-        <v>-137.452</v>
+        <v>-126.921</v>
       </c>
       <c r="F10">
-        <v>84.24799999999999</v>
+        <v>94.77899999999998</v>
       </c>
       <c r="G10">
         <v>21.7</v>
@@ -2107,28 +2107,28 @@
         <v>62.75</v>
       </c>
       <c r="M10">
-        <v>4.2376744</v>
+        <v>4.767383699999999</v>
       </c>
       <c r="N10">
-        <v>58.5123256</v>
+        <v>57.9826163</v>
       </c>
       <c r="O10">
-        <v>11.70246512</v>
+        <v>11.59652326</v>
       </c>
       <c r="P10">
-        <v>46.80986048</v>
+        <v>46.38609304000001</v>
       </c>
       <c r="Q10">
-        <v>84.30986048</v>
+        <v>83.88609304000001</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09996050879153909</v>
+        <v>0.1004443871868892</v>
       </c>
       <c r="T10">
-        <v>1.02740483822932</v>
+        <v>1.036583832584983</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>14.80765015830381</v>
+        <v>13.16235569627006</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09502599234006918</v>
+        <v>0.09498911659192241</v>
       </c>
       <c r="C11">
-        <v>967.462712144403</v>
+        <v>957.5518924183386</v>
       </c>
       <c r="D11">
-        <v>1040.541712144403</v>
+        <v>1041.161892418339</v>
       </c>
       <c r="E11">
-        <v>-126.921</v>
+        <v>-116.39</v>
       </c>
       <c r="F11">
-        <v>94.77899999999998</v>
+        <v>105.31</v>
       </c>
       <c r="G11">
         <v>21.7</v>
@@ -2189,45 +2189,45 @@
         <v>62.75</v>
       </c>
       <c r="M11">
-        <v>4.767383699999999</v>
+        <v>5.455057999999999</v>
       </c>
       <c r="N11">
-        <v>57.9826163</v>
+        <v>57.294942</v>
       </c>
       <c r="O11">
-        <v>11.59652326</v>
+        <v>11.4589884</v>
       </c>
       <c r="P11">
-        <v>46.38609304000001</v>
+        <v>45.8359536</v>
       </c>
       <c r="Q11">
-        <v>83.88609304000001</v>
+        <v>83.3359536</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1004443871868892</v>
+        <v>0.1009390184354693</v>
       </c>
       <c r="T11">
-        <v>1.036583832584983</v>
+        <v>1.045966804592993</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.16235569627006</v>
+        <v>11.50308576004142</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09498911659192241</v>
+        <v>0.09484424084377562</v>
       </c>
       <c r="C12">
-        <v>957.5518924183386</v>
+        <v>949.4646026521226</v>
       </c>
       <c r="D12">
-        <v>1041.161892418339</v>
+        <v>1043.605602652123</v>
       </c>
       <c r="E12">
-        <v>-116.39</v>
+        <v>-105.859</v>
       </c>
       <c r="F12">
-        <v>105.31</v>
+        <v>115.841</v>
       </c>
       <c r="G12">
         <v>21.7</v>
@@ -2271,28 +2271,28 @@
         <v>62.75</v>
       </c>
       <c r="M12">
-        <v>5.455058</v>
+        <v>6.000563799999999</v>
       </c>
       <c r="N12">
-        <v>57.294942</v>
+        <v>56.7494362</v>
       </c>
       <c r="O12">
-        <v>11.4589884</v>
+        <v>11.34988724</v>
       </c>
       <c r="P12">
-        <v>45.8359536</v>
+        <v>45.39954896</v>
       </c>
       <c r="Q12">
-        <v>83.3359536</v>
+        <v>82.89954896</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1009390184354693</v>
+        <v>0.1014447649930063</v>
       </c>
       <c r="T12">
-        <v>1.045966804592994</v>
+        <v>1.055560629904555</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.50308576004141</v>
+        <v>10.45735069094674</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09484424084377562</v>
+        <v>0.09486256509562885</v>
       </c>
       <c r="C13">
-        <v>949.4646026521226</v>
+        <v>938.6238824761512</v>
       </c>
       <c r="D13">
-        <v>1043.605602652123</v>
+        <v>1043.295882476151</v>
       </c>
       <c r="E13">
-        <v>-105.859</v>
+        <v>-95.328</v>
       </c>
       <c r="F13">
-        <v>115.841</v>
+        <v>126.372</v>
       </c>
       <c r="G13">
         <v>21.7</v>
@@ -2353,45 +2353,45 @@
         <v>62.75</v>
       </c>
       <c r="M13">
-        <v>6.000563799999999</v>
+        <v>6.760901999999999</v>
       </c>
       <c r="N13">
-        <v>56.7494362</v>
+        <v>55.989098</v>
       </c>
       <c r="O13">
-        <v>11.34988724</v>
+        <v>11.1978196</v>
       </c>
       <c r="P13">
-        <v>45.39954896</v>
+        <v>44.7912784</v>
       </c>
       <c r="Q13">
-        <v>82.89954896</v>
+        <v>82.2912784</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1014447649930063</v>
+        <v>0.1019620057904873</v>
       </c>
       <c r="T13">
-        <v>1.055560629904555</v>
+        <v>1.06537249670047</v>
       </c>
       <c r="U13">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y13">
-        <v>10.45735069094674</v>
+        <v>9.281305955921267</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09486256509562885</v>
+        <v>0.09473128934748207</v>
       </c>
       <c r="C14">
-        <v>938.6238824761512</v>
+        <v>930.3157991904798</v>
       </c>
       <c r="D14">
-        <v>1043.295882476151</v>
+        <v>1045.51879919048</v>
       </c>
       <c r="E14">
-        <v>-95.328</v>
+        <v>-84.797</v>
       </c>
       <c r="F14">
-        <v>126.372</v>
+        <v>136.903</v>
       </c>
       <c r="G14">
         <v>21.7</v>
@@ -2435,28 +2435,28 @@
         <v>62.75</v>
       </c>
       <c r="M14">
-        <v>6.760901999999999</v>
+        <v>7.324310499999999</v>
       </c>
       <c r="N14">
-        <v>55.989098</v>
+        <v>55.4256895</v>
       </c>
       <c r="O14">
-        <v>11.1978196</v>
+        <v>11.0851379</v>
       </c>
       <c r="P14">
-        <v>44.7912784</v>
+        <v>44.3405516</v>
       </c>
       <c r="Q14">
-        <v>82.2912784</v>
+        <v>81.8405516</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1019620057904873</v>
+        <v>0.1024911371810139</v>
       </c>
       <c r="T14">
-        <v>1.06537249670047</v>
+        <v>1.075409923652613</v>
       </c>
       <c r="U14">
         <v>0.0535</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>9.281305955921267</v>
+        <v>8.567359343927324</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09473128934748207</v>
+        <v>0.09460001359933529</v>
       </c>
       <c r="C15">
-        <v>930.3157991904798</v>
+        <v>922.0172087240082</v>
       </c>
       <c r="D15">
-        <v>1045.51879919048</v>
+        <v>1047.751208724008</v>
       </c>
       <c r="E15">
-        <v>-84.797</v>
+        <v>-74.26599999999999</v>
       </c>
       <c r="F15">
-        <v>136.903</v>
+        <v>147.434</v>
       </c>
       <c r="G15">
         <v>21.7</v>
@@ -2517,28 +2517,28 @@
         <v>62.75</v>
       </c>
       <c r="M15">
-        <v>7.324310499999999</v>
+        <v>7.887719</v>
       </c>
       <c r="N15">
-        <v>55.4256895</v>
+        <v>54.862281</v>
       </c>
       <c r="O15">
-        <v>11.0851379</v>
+        <v>10.9724562</v>
       </c>
       <c r="P15">
-        <v>44.3405516</v>
+        <v>43.8898248</v>
       </c>
       <c r="Q15">
-        <v>81.8405516</v>
+        <v>81.3898248</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1024911371810139</v>
+        <v>0.1030325739527155</v>
       </c>
       <c r="T15">
-        <v>1.075409923652613</v>
+        <v>1.085680779138527</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.567359343927324</v>
+        <v>7.955405105075371</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09460001359933529</v>
+        <v>0.0945647378511885</v>
       </c>
       <c r="C16">
-        <v>922.0172087240082</v>
+        <v>912.0877164063423</v>
       </c>
       <c r="D16">
-        <v>1047.751208724008</v>
+        <v>1048.352716406342</v>
       </c>
       <c r="E16">
-        <v>-74.26599999999999</v>
+        <v>-63.73499999999999</v>
       </c>
       <c r="F16">
-        <v>147.434</v>
+        <v>157.965</v>
       </c>
       <c r="G16">
         <v>21.7</v>
@@ -2599,45 +2599,45 @@
         <v>62.75</v>
       </c>
       <c r="M16">
-        <v>7.887719</v>
+        <v>8.5774995</v>
       </c>
       <c r="N16">
-        <v>54.862281</v>
+        <v>54.1725005</v>
       </c>
       <c r="O16">
-        <v>10.9724562</v>
+        <v>10.8345001</v>
       </c>
       <c r="P16">
-        <v>43.8898248</v>
+        <v>43.3380004</v>
       </c>
       <c r="Q16">
-        <v>81.3898248</v>
+        <v>80.8380004</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1030325739527155</v>
+        <v>0.1035867504131629</v>
       </c>
       <c r="T16">
-        <v>1.085680779138527</v>
+        <v>1.096193301812345</v>
       </c>
       <c r="U16">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V16">
         <v>0.2</v>
       </c>
       <c r="W16">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y16">
-        <v>7.955405105075371</v>
+        <v>7.315651840026338</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09456473785118849</v>
+        <v>0.09443986210304171</v>
       </c>
       <c r="C17">
-        <v>912.0877164063427</v>
+        <v>903.6916079226284</v>
       </c>
       <c r="D17">
-        <v>1048.352716406343</v>
+        <v>1050.487607922628</v>
       </c>
       <c r="E17">
-        <v>-63.73500000000001</v>
+        <v>-53.20400000000001</v>
       </c>
       <c r="F17">
-        <v>157.965</v>
+        <v>168.496</v>
       </c>
       <c r="G17">
         <v>21.7</v>
@@ -2681,28 +2681,28 @@
         <v>62.75</v>
       </c>
       <c r="M17">
-        <v>8.577499499999998</v>
+        <v>9.1493328</v>
       </c>
       <c r="N17">
-        <v>54.1725005</v>
+        <v>53.6006672</v>
       </c>
       <c r="O17">
-        <v>10.8345001</v>
+        <v>10.72013344</v>
       </c>
       <c r="P17">
-        <v>43.3380004</v>
+        <v>42.88053376000001</v>
       </c>
       <c r="Q17">
-        <v>80.8380004</v>
+        <v>80.38053376000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1035867504131629</v>
+        <v>0.1041541215512401</v>
       </c>
       <c r="T17">
-        <v>1.096193301812345</v>
+        <v>1.106956122645063</v>
       </c>
       <c r="U17">
         <v>0.0543</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>7.31565184002634</v>
+        <v>6.858423600024693</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09443986210304171</v>
+        <v>0.09431498635489494</v>
       </c>
       <c r="C18">
-        <v>903.6916079226284</v>
+        <v>895.3042122741917</v>
       </c>
       <c r="D18">
-        <v>1050.487607922628</v>
+        <v>1052.631212274192</v>
       </c>
       <c r="E18">
-        <v>-53.20400000000001</v>
+        <v>-42.673</v>
       </c>
       <c r="F18">
-        <v>168.496</v>
+        <v>179.027</v>
       </c>
       <c r="G18">
         <v>21.7</v>
@@ -2763,28 +2763,28 @@
         <v>62.75</v>
       </c>
       <c r="M18">
-        <v>9.1493328</v>
+        <v>9.7211661</v>
       </c>
       <c r="N18">
-        <v>53.6006672</v>
+        <v>53.0288339</v>
       </c>
       <c r="O18">
-        <v>10.72013344</v>
+        <v>10.60576678</v>
       </c>
       <c r="P18">
-        <v>42.88053376000001</v>
+        <v>42.42306712</v>
       </c>
       <c r="Q18">
-        <v>80.38053376000001</v>
+        <v>79.92306712</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1041541215512401</v>
+        <v>0.104735164283006</v>
       </c>
       <c r="T18">
-        <v>1.106956122645063</v>
+        <v>1.117978288558088</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>6.858423600024693</v>
+        <v>6.4549869176703</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09431498635489494</v>
+        <v>0.09433411060674818</v>
       </c>
       <c r="C19">
-        <v>895.3042122741917</v>
+        <v>884.4443601949572</v>
       </c>
       <c r="D19">
-        <v>1052.631212274192</v>
+        <v>1052.302360194957</v>
       </c>
       <c r="E19">
-        <v>-42.673</v>
+        <v>-32.142</v>
       </c>
       <c r="F19">
-        <v>179.027</v>
+        <v>189.558</v>
       </c>
       <c r="G19">
         <v>21.7</v>
@@ -2845,45 +2845,45 @@
         <v>62.75</v>
       </c>
       <c r="M19">
-        <v>9.7211661</v>
+        <v>10.4825574</v>
       </c>
       <c r="N19">
-        <v>53.0288339</v>
+        <v>52.2674426</v>
       </c>
       <c r="O19">
-        <v>10.60576678</v>
+        <v>10.45348852</v>
       </c>
       <c r="P19">
-        <v>42.42306712</v>
+        <v>41.81395408</v>
       </c>
       <c r="Q19">
-        <v>79.92306712</v>
+        <v>79.31395408</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.104735164283006</v>
+        <v>0.1053303787887173</v>
       </c>
       <c r="T19">
-        <v>1.117978288558088</v>
+        <v>1.129269287786064</v>
       </c>
       <c r="U19">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V19">
         <v>0.2</v>
       </c>
       <c r="W19">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y19">
-        <v>6.4549869176703</v>
+        <v>5.986134643059527</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09433411060674816</v>
+        <v>0.0942172348586014</v>
       </c>
       <c r="C20">
-        <v>884.4443601949574</v>
+        <v>875.9263186645048</v>
       </c>
       <c r="D20">
-        <v>1052.302360194957</v>
+        <v>1054.315318664505</v>
       </c>
       <c r="E20">
-        <v>-32.14200000000002</v>
+        <v>-21.61099999999999</v>
       </c>
       <c r="F20">
-        <v>189.558</v>
+        <v>200.089</v>
       </c>
       <c r="G20">
         <v>21.7</v>
@@ -2927,28 +2927,28 @@
         <v>62.75</v>
       </c>
       <c r="M20">
-        <v>10.4825574</v>
+        <v>11.0649217</v>
       </c>
       <c r="N20">
-        <v>52.2674426</v>
+        <v>51.6850783</v>
       </c>
       <c r="O20">
-        <v>10.45348852</v>
+        <v>10.33701566</v>
       </c>
       <c r="P20">
-        <v>41.81395408</v>
+        <v>41.34806264</v>
       </c>
       <c r="Q20">
-        <v>79.31395408</v>
+        <v>78.84806263999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1053303787887173</v>
+        <v>0.1059402899488906</v>
       </c>
       <c r="T20">
-        <v>1.129269287786064</v>
+        <v>1.140839077118435</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>5.986134643059527</v>
+        <v>5.671074925003762</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.0942172348586014</v>
+        <v>0.09410035911045458</v>
       </c>
       <c r="C21">
-        <v>875.9263186645048</v>
+        <v>867.4159931060384</v>
       </c>
       <c r="D21">
-        <v>1054.315318664505</v>
+        <v>1056.335993106038</v>
       </c>
       <c r="E21">
-        <v>-21.61099999999999</v>
+        <v>-11.07999999999998</v>
       </c>
       <c r="F21">
-        <v>200.089</v>
+        <v>210.62</v>
       </c>
       <c r="G21">
         <v>21.7</v>
@@ -3009,28 +3009,28 @@
         <v>62.75</v>
       </c>
       <c r="M21">
-        <v>11.0649217</v>
+        <v>11.647286</v>
       </c>
       <c r="N21">
-        <v>51.6850783</v>
+        <v>51.102714</v>
       </c>
       <c r="O21">
-        <v>10.33701566</v>
+        <v>10.2205428</v>
       </c>
       <c r="P21">
-        <v>41.34806264</v>
+        <v>40.8821712</v>
       </c>
       <c r="Q21">
-        <v>78.84806263999999</v>
+        <v>78.3821712</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1059402899488906</v>
+        <v>0.1065654488880682</v>
       </c>
       <c r="T21">
-        <v>1.140839077118435</v>
+        <v>1.152698111184115</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.671074925003762</v>
+        <v>5.387521178753573</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09410035911045458</v>
+        <v>0.09398348336230783</v>
       </c>
       <c r="C22">
-        <v>867.4159931060384</v>
+        <v>858.9134279694661</v>
       </c>
       <c r="D22">
-        <v>1056.335993106038</v>
+        <v>1058.364427969466</v>
       </c>
       <c r="E22">
-        <v>-11.07999999999998</v>
+        <v>-0.5489999999999782</v>
       </c>
       <c r="F22">
-        <v>210.62</v>
+        <v>221.151</v>
       </c>
       <c r="G22">
         <v>21.7</v>
@@ -3091,28 +3091,28 @@
         <v>62.75</v>
       </c>
       <c r="M22">
-        <v>11.647286</v>
+        <v>12.2296503</v>
       </c>
       <c r="N22">
-        <v>51.102714</v>
+        <v>50.5203497</v>
       </c>
       <c r="O22">
-        <v>10.2205428</v>
+        <v>10.10406994</v>
       </c>
       <c r="P22">
-        <v>40.8821712</v>
+        <v>40.41627975999999</v>
       </c>
       <c r="Q22">
-        <v>78.3821712</v>
+        <v>77.91627975999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1065654488880682</v>
+        <v>0.1072064346358327</v>
       </c>
       <c r="T22">
-        <v>1.152698111184115</v>
+        <v>1.164857373960319</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.387521178753573</v>
+        <v>5.13097255119388</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09398348336230783</v>
+        <v>0.09386660761416105</v>
       </c>
       <c r="C23">
-        <v>858.9134279694662</v>
+        <v>850.4186680467774</v>
       </c>
       <c r="D23">
-        <v>1058.364427969466</v>
+        <v>1060.400668046777</v>
       </c>
       <c r="E23">
-        <v>-0.5490000000000066</v>
+        <v>9.981999999999999</v>
       </c>
       <c r="F23">
-        <v>221.151</v>
+        <v>231.682</v>
       </c>
       <c r="G23">
         <v>21.7</v>
@@ -3173,28 +3173,28 @@
         <v>62.75</v>
       </c>
       <c r="M23">
-        <v>12.2296503</v>
+        <v>12.8120146</v>
       </c>
       <c r="N23">
-        <v>50.5203497</v>
+        <v>49.9379854</v>
       </c>
       <c r="O23">
-        <v>10.10406994</v>
+        <v>9.98759708</v>
       </c>
       <c r="P23">
-        <v>40.41627975999999</v>
+        <v>39.95038832</v>
       </c>
       <c r="Q23">
-        <v>77.91627975999999</v>
+        <v>77.45038832</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1072064346358327</v>
+        <v>0.1078638559155911</v>
       </c>
       <c r="T23">
-        <v>1.164857373960319</v>
+        <v>1.177328412705143</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.13097255119388</v>
+        <v>4.897746526139613</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09386660761416105</v>
+        <v>0.09374973186601425</v>
       </c>
       <c r="C24">
-        <v>850.4186680467774</v>
+        <v>841.9317584753339</v>
       </c>
       <c r="D24">
-        <v>1060.400668046777</v>
+        <v>1062.444758475334</v>
       </c>
       <c r="E24">
-        <v>9.981999999999999</v>
+        <v>20.51300000000001</v>
       </c>
       <c r="F24">
-        <v>231.682</v>
+        <v>242.213</v>
       </c>
       <c r="G24">
         <v>21.7</v>
@@ -3255,28 +3255,28 @@
         <v>62.75</v>
       </c>
       <c r="M24">
-        <v>12.8120146</v>
+        <v>13.3943789</v>
       </c>
       <c r="N24">
-        <v>49.9379854</v>
+        <v>49.3556211</v>
       </c>
       <c r="O24">
-        <v>9.98759708</v>
+        <v>9.87112422</v>
       </c>
       <c r="P24">
-        <v>39.95038832</v>
+        <v>39.48449688</v>
       </c>
       <c r="Q24">
-        <v>77.45038832</v>
+        <v>76.98449687999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1078638559155911</v>
+        <v>0.1085383530727458</v>
       </c>
       <c r="T24">
-        <v>1.177328412705143</v>
+        <v>1.190123374534249</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>4.897746526139613</v>
+        <v>4.684801025003107</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09374973186601425</v>
+        <v>0.09411285611786747</v>
       </c>
       <c r="C25">
-        <v>841.9317584753339</v>
+        <v>825.0755615698596</v>
       </c>
       <c r="D25">
-        <v>1062.444758475334</v>
+        <v>1056.11956156986</v>
       </c>
       <c r="E25">
-        <v>20.51300000000001</v>
+        <v>31.04400000000001</v>
       </c>
       <c r="F25">
-        <v>242.213</v>
+        <v>252.744</v>
       </c>
       <c r="G25">
         <v>21.7</v>
@@ -3337,45 +3337,45 @@
         <v>62.75</v>
       </c>
       <c r="M25">
-        <v>13.3943789</v>
+        <v>14.6086032</v>
       </c>
       <c r="N25">
-        <v>49.3556211</v>
+        <v>48.1413968</v>
       </c>
       <c r="O25">
-        <v>9.87112422</v>
+        <v>9.628279360000001</v>
       </c>
       <c r="P25">
-        <v>39.48449688</v>
+        <v>38.51311743999999</v>
       </c>
       <c r="Q25">
-        <v>76.98449687999999</v>
+        <v>76.01311744</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1085383530727458</v>
+        <v>0.1092306001550888</v>
       </c>
       <c r="T25">
-        <v>1.190123374534249</v>
+        <v>1.203255045885173</v>
       </c>
       <c r="U25">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V25">
         <v>0.2</v>
       </c>
       <c r="W25">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y25">
-        <v>4.684801025003107</v>
+        <v>4.295414088596779</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09411285611786747</v>
+        <v>0.09401598036972071</v>
       </c>
       <c r="C26">
-        <v>825.0755615698597</v>
+        <v>816.2246452880896</v>
       </c>
       <c r="D26">
-        <v>1056.11956156986</v>
+        <v>1057.79964528809</v>
       </c>
       <c r="E26">
-        <v>31.04399999999998</v>
+        <v>41.57499999999999</v>
       </c>
       <c r="F26">
-        <v>252.744</v>
+        <v>263.275</v>
       </c>
       <c r="G26">
         <v>21.7</v>
@@ -3419,28 +3419,28 @@
         <v>62.75</v>
       </c>
       <c r="M26">
-        <v>14.6086032</v>
+        <v>15.217295</v>
       </c>
       <c r="N26">
-        <v>48.1413968</v>
+        <v>47.532705</v>
       </c>
       <c r="O26">
-        <v>9.628279360000001</v>
+        <v>9.506541</v>
       </c>
       <c r="P26">
-        <v>38.51311744</v>
+        <v>38.026164</v>
       </c>
       <c r="Q26">
-        <v>76.01311744</v>
+        <v>75.52616399999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1092306001550888</v>
+        <v>0.1099413071596276</v>
       </c>
       <c r="T26">
-        <v>1.203255045885173</v>
+        <v>1.216736895138788</v>
       </c>
       <c r="U26">
         <v>0.0578</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>4.295414088596781</v>
+        <v>4.123597525052908</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09401598036972071</v>
+        <v>0.0946471046215739</v>
       </c>
       <c r="C27">
-        <v>816.2246452880896</v>
+        <v>794.8433067324534</v>
       </c>
       <c r="D27">
-        <v>1057.79964528809</v>
+        <v>1046.949306732453</v>
       </c>
       <c r="E27">
-        <v>41.57499999999999</v>
+        <v>52.10599999999999</v>
       </c>
       <c r="F27">
-        <v>263.275</v>
+        <v>273.806</v>
       </c>
       <c r="G27">
         <v>21.7</v>
@@ -3501,45 +3501,45 @@
         <v>62.75</v>
       </c>
       <c r="M27">
-        <v>15.217295</v>
+        <v>16.7843078</v>
       </c>
       <c r="N27">
-        <v>47.532705</v>
+        <v>45.9656922</v>
       </c>
       <c r="O27">
-        <v>9.506541</v>
+        <v>9.19313844</v>
       </c>
       <c r="P27">
-        <v>38.026164</v>
+        <v>36.77255376</v>
       </c>
       <c r="Q27">
-        <v>75.52616399999999</v>
+        <v>74.27255375999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1099413071596276</v>
+        <v>0.1106712224615864</v>
       </c>
       <c r="T27">
-        <v>1.216736895138788</v>
+        <v>1.230583118696555</v>
       </c>
       <c r="U27">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>4.123597525052908</v>
+        <v>3.738611132953603</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.0946471046215739</v>
+        <v>0.09457822887342714</v>
       </c>
       <c r="C28">
-        <v>794.8433067324534</v>
+        <v>785.4855914523027</v>
       </c>
       <c r="D28">
-        <v>1046.949306732453</v>
+        <v>1048.122591452303</v>
       </c>
       <c r="E28">
-        <v>52.10599999999999</v>
+        <v>62.637</v>
       </c>
       <c r="F28">
-        <v>273.806</v>
+        <v>284.337</v>
       </c>
       <c r="G28">
         <v>21.7</v>
@@ -3583,28 +3583,28 @@
         <v>62.75</v>
       </c>
       <c r="M28">
-        <v>16.7843078</v>
+        <v>17.4298581</v>
       </c>
       <c r="N28">
-        <v>45.9656922</v>
+        <v>45.3201419</v>
       </c>
       <c r="O28">
-        <v>9.19313844</v>
+        <v>9.06402838</v>
       </c>
       <c r="P28">
-        <v>36.77255376</v>
+        <v>36.25611352</v>
       </c>
       <c r="Q28">
-        <v>74.27255375999999</v>
+        <v>73.75611352</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1106712224615864</v>
+        <v>0.1114211354430509</v>
       </c>
       <c r="T28">
-        <v>1.230583118696555</v>
+        <v>1.244808690844946</v>
       </c>
       <c r="U28">
         <v>0.0613</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>3.738611132953603</v>
+        <v>3.600144053955321</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09457822887342714</v>
+        <v>0.09513655312528038</v>
       </c>
       <c r="C29">
-        <v>785.4855914523027</v>
+        <v>765.5187094989085</v>
       </c>
       <c r="D29">
-        <v>1048.122591452303</v>
+        <v>1038.686709498908</v>
       </c>
       <c r="E29">
-        <v>62.637</v>
+        <v>73.16800000000001</v>
       </c>
       <c r="F29">
-        <v>284.337</v>
+        <v>294.868</v>
       </c>
       <c r="G29">
         <v>21.7</v>
@@ -3665,45 +3665,45 @@
         <v>62.75</v>
       </c>
       <c r="M29">
-        <v>17.4298581</v>
+        <v>18.9010388</v>
       </c>
       <c r="N29">
-        <v>45.3201419</v>
+        <v>43.8489612</v>
       </c>
       <c r="O29">
-        <v>9.06402838</v>
+        <v>8.769792239999999</v>
       </c>
       <c r="P29">
-        <v>36.25611352</v>
+        <v>35.07916896</v>
       </c>
       <c r="Q29">
-        <v>73.75611352</v>
+        <v>72.57916896</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1114211354430509</v>
+        <v>0.1121918793406672</v>
       </c>
       <c r="T29">
-        <v>1.244808690844946</v>
+        <v>1.259429417775237</v>
       </c>
       <c r="U29">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V29">
         <v>0.2</v>
       </c>
       <c r="W29">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y29">
-        <v>3.600144053955321</v>
+        <v>3.319923347281843</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09513655312528038</v>
+        <v>0.09509007737713357</v>
       </c>
       <c r="C30">
-        <v>765.5187094989085</v>
+        <v>755.766679025692</v>
       </c>
       <c r="D30">
-        <v>1038.686709498908</v>
+        <v>1039.465679025692</v>
       </c>
       <c r="E30">
-        <v>73.16800000000001</v>
+        <v>83.69900000000001</v>
       </c>
       <c r="F30">
-        <v>294.868</v>
+        <v>305.399</v>
       </c>
       <c r="G30">
         <v>21.7</v>
@@ -3747,28 +3747,28 @@
         <v>62.75</v>
       </c>
       <c r="M30">
-        <v>18.9010388</v>
+        <v>19.5760759</v>
       </c>
       <c r="N30">
-        <v>43.8489612</v>
+        <v>43.17392409999999</v>
       </c>
       <c r="O30">
-        <v>8.769792239999999</v>
+        <v>8.634784819999998</v>
       </c>
       <c r="P30">
-        <v>35.07916896</v>
+        <v>34.53913927999999</v>
       </c>
       <c r="Q30">
-        <v>72.57916896</v>
+        <v>72.03913928</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1121918793406672</v>
+        <v>0.1129843343339909</v>
       </c>
       <c r="T30">
-        <v>1.259429417775237</v>
+        <v>1.274461996168353</v>
       </c>
       <c r="U30">
         <v>0.0641</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>3.319923347281843</v>
+        <v>3.205443231858331</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09509007737713357</v>
+        <v>0.09504360162898678</v>
       </c>
       <c r="C31">
-        <v>755.7666790256922</v>
+        <v>746.0158178154076</v>
       </c>
       <c r="D31">
-        <v>1039.465679025692</v>
+        <v>1040.245817815407</v>
       </c>
       <c r="E31">
-        <v>83.69899999999996</v>
+        <v>94.22999999999996</v>
       </c>
       <c r="F31">
-        <v>305.3989999999999</v>
+        <v>315.9299999999999</v>
       </c>
       <c r="G31">
         <v>21.7</v>
@@ -3829,28 +3829,28 @@
         <v>62.75</v>
       </c>
       <c r="M31">
-        <v>19.5760759</v>
+        <v>20.251113</v>
       </c>
       <c r="N31">
-        <v>43.1739241</v>
+        <v>42.498887</v>
       </c>
       <c r="O31">
-        <v>8.63478482</v>
+        <v>8.499777400000001</v>
       </c>
       <c r="P31">
-        <v>34.53913928</v>
+        <v>33.9991096</v>
       </c>
       <c r="Q31">
-        <v>72.03913928</v>
+        <v>71.4991096</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1129843343339909</v>
+        <v>0.1137994308985526</v>
       </c>
       <c r="T31">
-        <v>1.274461996168353</v>
+        <v>1.289924076801272</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.205443231858332</v>
+        <v>3.098595124129721</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09504360162898678</v>
+        <v>0.09693152588084002</v>
       </c>
       <c r="C32">
-        <v>746.0158178154076</v>
+        <v>704.7087450057952</v>
       </c>
       <c r="D32">
-        <v>1040.245817815407</v>
+        <v>1009.469745005795</v>
       </c>
       <c r="E32">
-        <v>94.22999999999996</v>
+        <v>104.761</v>
       </c>
       <c r="F32">
-        <v>315.9299999999999</v>
+        <v>326.461</v>
       </c>
       <c r="G32">
         <v>21.7</v>
@@ -3911,45 +3911,45 @@
         <v>62.75</v>
       </c>
       <c r="M32">
-        <v>20.251113</v>
+        <v>23.4725459</v>
       </c>
       <c r="N32">
-        <v>42.498887</v>
+        <v>39.2774541</v>
       </c>
       <c r="O32">
-        <v>8.499777400000001</v>
+        <v>7.85549082</v>
       </c>
       <c r="P32">
-        <v>33.9991096</v>
+        <v>31.42196328</v>
       </c>
       <c r="Q32">
-        <v>71.4991096</v>
+        <v>68.92196328</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1137994308985526</v>
+        <v>0.1146381534504928</v>
       </c>
       <c r="T32">
-        <v>1.289924076801272</v>
+        <v>1.30583433368442</v>
       </c>
       <c r="U32">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y32">
-        <v>3.098595124129721</v>
+        <v>2.67333591623736</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09693152588084002</v>
+        <v>0.09694745013269324</v>
       </c>
       <c r="C33">
-        <v>704.7087450057952</v>
+        <v>693.9258980889288</v>
       </c>
       <c r="D33">
-        <v>1009.469745005795</v>
+        <v>1009.217898088929</v>
       </c>
       <c r="E33">
-        <v>104.761</v>
+        <v>115.292</v>
       </c>
       <c r="F33">
-        <v>326.461</v>
+        <v>336.992</v>
       </c>
       <c r="G33">
         <v>21.7</v>
@@ -3993,28 +3993,28 @@
         <v>62.75</v>
       </c>
       <c r="M33">
-        <v>23.4725459</v>
+        <v>24.2297248</v>
       </c>
       <c r="N33">
-        <v>39.2774541</v>
+        <v>38.5202752</v>
       </c>
       <c r="O33">
-        <v>7.85549082</v>
+        <v>7.70405504</v>
       </c>
       <c r="P33">
-        <v>31.42196328</v>
+        <v>30.81622016</v>
       </c>
       <c r="Q33">
-        <v>68.92196328</v>
+        <v>68.31622016</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1146381534504928</v>
+        <v>0.1155015443127842</v>
       </c>
       <c r="T33">
-        <v>1.30583433368442</v>
+        <v>1.322212539299426</v>
       </c>
       <c r="U33">
         <v>0.07190000000000001</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>2.67333591623736</v>
+        <v>2.589794168854943</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09694745013269324</v>
+        <v>0.09696337438454646</v>
       </c>
       <c r="C34">
-        <v>693.9258980889288</v>
+        <v>683.1431768044545</v>
       </c>
       <c r="D34">
-        <v>1009.217898088929</v>
+        <v>1008.966176804454</v>
       </c>
       <c r="E34">
-        <v>115.292</v>
+        <v>125.823</v>
       </c>
       <c r="F34">
-        <v>336.992</v>
+        <v>347.523</v>
       </c>
       <c r="G34">
         <v>21.7</v>
@@ -4075,28 +4075,28 @@
         <v>62.75</v>
       </c>
       <c r="M34">
-        <v>24.2297248</v>
+        <v>24.9869037</v>
       </c>
       <c r="N34">
-        <v>38.5202752</v>
+        <v>37.7630963</v>
       </c>
       <c r="O34">
-        <v>7.70405504</v>
+        <v>7.55261926</v>
       </c>
       <c r="P34">
-        <v>30.81622016</v>
+        <v>30.21047704</v>
       </c>
       <c r="Q34">
-        <v>68.31622016</v>
+        <v>67.71047704</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1155015443127842</v>
+        <v>0.1163907080366365</v>
       </c>
       <c r="T34">
-        <v>1.322212539299426</v>
+        <v>1.339079646574582</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.589794168854943</v>
+        <v>2.511315557677521</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09696337438454646</v>
+        <v>0.09804009863639966</v>
       </c>
       <c r="C35">
-        <v>683.1431768044545</v>
+        <v>655.8784043630926</v>
       </c>
       <c r="D35">
-        <v>1008.966176804454</v>
+        <v>992.2324043630925</v>
       </c>
       <c r="E35">
-        <v>125.823</v>
+        <v>136.354</v>
       </c>
       <c r="F35">
-        <v>347.523</v>
+        <v>358.054</v>
       </c>
       <c r="G35">
         <v>21.7</v>
@@ -4157,45 +4157,45 @@
         <v>62.75</v>
       </c>
       <c r="M35">
-        <v>24.9869037</v>
+        <v>27.1404932</v>
       </c>
       <c r="N35">
-        <v>37.7630963</v>
+        <v>35.6095068</v>
       </c>
       <c r="O35">
-        <v>7.55261926</v>
+        <v>7.12190136</v>
       </c>
       <c r="P35">
-        <v>30.21047704</v>
+        <v>28.48760544</v>
       </c>
       <c r="Q35">
-        <v>67.71047704</v>
+        <v>65.98760544</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1163907080366365</v>
+        <v>0.1173068161157571</v>
       </c>
       <c r="T35">
-        <v>1.339079646574582</v>
+        <v>1.35645787831262</v>
       </c>
       <c r="U35">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y35">
-        <v>2.511315557677521</v>
+        <v>2.312043467213043</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09804009863639966</v>
+        <v>0.09808722288825289</v>
       </c>
       <c r="C36">
-        <v>655.8784043630926</v>
+        <v>644.627697731112</v>
       </c>
       <c r="D36">
-        <v>992.2324043630925</v>
+        <v>991.5126977311119</v>
       </c>
       <c r="E36">
-        <v>136.354</v>
+        <v>146.885</v>
       </c>
       <c r="F36">
-        <v>358.054</v>
+        <v>368.585</v>
       </c>
       <c r="G36">
         <v>21.7</v>
@@ -4239,28 +4239,28 @@
         <v>62.75</v>
       </c>
       <c r="M36">
-        <v>27.1404932</v>
+        <v>27.938743</v>
       </c>
       <c r="N36">
-        <v>35.6095068</v>
+        <v>34.811257</v>
       </c>
       <c r="O36">
-        <v>7.12190136</v>
+        <v>6.9622514</v>
       </c>
       <c r="P36">
-        <v>28.48760544</v>
+        <v>27.8490056</v>
       </c>
       <c r="Q36">
-        <v>65.98760544</v>
+        <v>65.3490056</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1173068161157571</v>
+        <v>0.1182511121357737</v>
       </c>
       <c r="T36">
-        <v>1.35645787831262</v>
+        <v>1.374370824873368</v>
       </c>
       <c r="U36">
         <v>0.07580000000000001</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>2.312043467213043</v>
+        <v>2.245985082435527</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09808722288825289</v>
+        <v>0.0981343471401061</v>
       </c>
       <c r="C37">
-        <v>644.627697731112</v>
+        <v>633.3780344075254</v>
       </c>
       <c r="D37">
-        <v>991.5126977311119</v>
+        <v>990.7940344075254</v>
       </c>
       <c r="E37">
-        <v>146.885</v>
+        <v>157.416</v>
       </c>
       <c r="F37">
-        <v>368.585</v>
+        <v>379.116</v>
       </c>
       <c r="G37">
         <v>21.7</v>
@@ -4321,28 +4321,28 @@
         <v>62.75</v>
       </c>
       <c r="M37">
-        <v>27.938743</v>
+        <v>28.7369928</v>
       </c>
       <c r="N37">
-        <v>34.811257</v>
+        <v>34.0130072</v>
       </c>
       <c r="O37">
-        <v>6.9622514</v>
+        <v>6.80260144</v>
       </c>
       <c r="P37">
-        <v>27.8490056</v>
+        <v>27.21040576</v>
       </c>
       <c r="Q37">
-        <v>65.3490056</v>
+        <v>64.71040576</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1182511121357737</v>
+        <v>0.1192249174064158</v>
       </c>
       <c r="T37">
-        <v>1.374370824873368</v>
+        <v>1.392843551014139</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.245985082435527</v>
+        <v>2.183596607923429</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09813434714010612</v>
+        <v>0.09818147139195935</v>
       </c>
       <c r="C38">
-        <v>633.3780344075253</v>
+        <v>622.1294121253588</v>
       </c>
       <c r="D38">
-        <v>990.7940344075251</v>
+        <v>990.0764121253587</v>
       </c>
       <c r="E38">
-        <v>157.4159999999999</v>
+        <v>167.9469999999999</v>
       </c>
       <c r="F38">
-        <v>379.1159999999999</v>
+        <v>389.6469999999999</v>
       </c>
       <c r="G38">
         <v>21.7</v>
@@ -4403,28 +4403,28 @@
         <v>62.75</v>
       </c>
       <c r="M38">
-        <v>28.7369928</v>
+        <v>29.5352426</v>
       </c>
       <c r="N38">
-        <v>34.0130072</v>
+        <v>33.2147574</v>
       </c>
       <c r="O38">
-        <v>6.802601440000001</v>
+        <v>6.642951480000001</v>
       </c>
       <c r="P38">
-        <v>27.21040576</v>
+        <v>26.57180592</v>
       </c>
       <c r="Q38">
-        <v>64.71040576</v>
+        <v>64.07180592</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1192249174064158</v>
+        <v>0.1202296371300942</v>
       </c>
       <c r="T38">
-        <v>1.392843551014139</v>
+        <v>1.411902712905411</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.183596607923429</v>
+        <v>2.124580483384958</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09818147139195935</v>
+        <v>0.09822859564381256</v>
       </c>
       <c r="C39">
-        <v>622.1294121253588</v>
+        <v>610.8818286242022</v>
       </c>
       <c r="D39">
-        <v>990.0764121253587</v>
+        <v>989.3598286242021</v>
       </c>
       <c r="E39">
-        <v>167.9469999999999</v>
+        <v>178.478</v>
       </c>
       <c r="F39">
-        <v>389.6469999999999</v>
+        <v>400.178</v>
       </c>
       <c r="G39">
         <v>21.7</v>
@@ -4485,28 +4485,28 @@
         <v>62.75</v>
       </c>
       <c r="M39">
-        <v>29.5352426</v>
+        <v>30.3334924</v>
       </c>
       <c r="N39">
-        <v>33.2147574</v>
+        <v>32.4165076</v>
       </c>
       <c r="O39">
-        <v>6.642951480000001</v>
+        <v>6.483301520000001</v>
       </c>
       <c r="P39">
-        <v>26.57180592</v>
+        <v>25.93320608</v>
       </c>
       <c r="Q39">
-        <v>64.07180592</v>
+        <v>63.43320608000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1202296371300942</v>
+        <v>0.1212667671674396</v>
       </c>
       <c r="T39">
-        <v>1.411902712905411</v>
+        <v>1.431576686470595</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.124580483384958</v>
+        <v>2.068670470664301</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09822859564381256</v>
+        <v>0.09827571989566579</v>
       </c>
       <c r="C40">
-        <v>610.8818286242022</v>
+        <v>599.6352816501833</v>
       </c>
       <c r="D40">
-        <v>989.3598286242021</v>
+        <v>988.6442816501833</v>
       </c>
       <c r="E40">
-        <v>178.478</v>
+        <v>189.009</v>
       </c>
       <c r="F40">
-        <v>400.178</v>
+        <v>410.709</v>
       </c>
       <c r="G40">
         <v>21.7</v>
@@ -4567,28 +4567,28 @@
         <v>62.75</v>
       </c>
       <c r="M40">
-        <v>30.3334924</v>
+        <v>31.1317422</v>
       </c>
       <c r="N40">
-        <v>32.4165076</v>
+        <v>31.6182578</v>
       </c>
       <c r="O40">
-        <v>6.483301520000001</v>
+        <v>6.32365156</v>
       </c>
       <c r="P40">
-        <v>25.93320608</v>
+        <v>25.29460624</v>
       </c>
       <c r="Q40">
-        <v>63.43320608000001</v>
+        <v>62.79460624</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1212667671674396</v>
+        <v>0.1223379014683046</v>
       </c>
       <c r="T40">
-        <v>1.431576686470595</v>
+        <v>1.451895708349391</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.068670470664301</v>
+        <v>2.015627638083165</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09827571989566579</v>
+        <v>0.102866844147519</v>
       </c>
       <c r="C41">
-        <v>599.6352816501833</v>
+        <v>524.0273558306836</v>
       </c>
       <c r="D41">
-        <v>988.6442816501833</v>
+        <v>923.5673558306836</v>
       </c>
       <c r="E41">
-        <v>189.009</v>
+        <v>199.54</v>
       </c>
       <c r="F41">
-        <v>410.709</v>
+        <v>421.24</v>
       </c>
       <c r="G41">
         <v>21.7</v>
@@ -4649,45 +4649,45 @@
         <v>62.75</v>
       </c>
       <c r="M41">
-        <v>31.1317422</v>
+        <v>37.9116</v>
       </c>
       <c r="N41">
-        <v>31.6182578</v>
+        <v>24.8384</v>
       </c>
       <c r="O41">
-        <v>6.32365156</v>
+        <v>4.967680000000001</v>
       </c>
       <c r="P41">
-        <v>25.29460624</v>
+        <v>19.87072</v>
       </c>
       <c r="Q41">
-        <v>62.79460624</v>
+        <v>57.37072</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1223379014683046</v>
+        <v>0.123444740245865</v>
       </c>
       <c r="T41">
-        <v>1.451895708349391</v>
+        <v>1.47289203095748</v>
       </c>
       <c r="U41">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V41">
         <v>0.2</v>
       </c>
       <c r="W41">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y41">
-        <v>2.015627638083165</v>
+        <v>1.655166228805959</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.102866844147519</v>
+        <v>0.1030275683993722</v>
       </c>
       <c r="C42">
-        <v>524.0273558306836</v>
+        <v>511.3730219306629</v>
       </c>
       <c r="D42">
-        <v>923.5673558306836</v>
+        <v>921.4440219306629</v>
       </c>
       <c r="E42">
-        <v>199.54</v>
+        <v>210.071</v>
       </c>
       <c r="F42">
-        <v>421.24</v>
+        <v>431.771</v>
       </c>
       <c r="G42">
         <v>21.7</v>
@@ -4731,28 +4731,28 @@
         <v>62.75</v>
       </c>
       <c r="M42">
-        <v>37.9116</v>
+        <v>38.85939</v>
       </c>
       <c r="N42">
-        <v>24.8384</v>
+        <v>23.89061</v>
       </c>
       <c r="O42">
-        <v>4.967680000000001</v>
+        <v>4.778122000000001</v>
       </c>
       <c r="P42">
-        <v>19.87072</v>
+        <v>19.112488</v>
       </c>
       <c r="Q42">
-        <v>57.37072</v>
+        <v>56.612488</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.123444740245865</v>
+        <v>0.1245890989819868</v>
       </c>
       <c r="T42">
-        <v>1.47289203095748</v>
+        <v>1.494600093314997</v>
       </c>
       <c r="U42">
         <v>0.09</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>1.655166228805959</v>
+        <v>1.614796320786302</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1030275683993722</v>
+        <v>0.1031882926512254</v>
       </c>
       <c r="C43">
-        <v>511.3730219306629</v>
+        <v>498.7284289665747</v>
       </c>
       <c r="D43">
-        <v>921.4440219306629</v>
+        <v>919.3304289665747</v>
       </c>
       <c r="E43">
-        <v>210.071</v>
+        <v>220.602</v>
       </c>
       <c r="F43">
-        <v>431.771</v>
+        <v>442.302</v>
       </c>
       <c r="G43">
         <v>21.7</v>
@@ -4813,28 +4813,28 @@
         <v>62.75</v>
       </c>
       <c r="M43">
-        <v>38.85939</v>
+        <v>39.80718</v>
       </c>
       <c r="N43">
-        <v>23.89061</v>
+        <v>22.94282</v>
       </c>
       <c r="O43">
-        <v>4.778122000000001</v>
+        <v>4.588564</v>
       </c>
       <c r="P43">
-        <v>19.112488</v>
+        <v>18.354256</v>
       </c>
       <c r="Q43">
-        <v>56.612488</v>
+        <v>55.854256</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1245890989819868</v>
+        <v>0.1257729183641818</v>
       </c>
       <c r="T43">
-        <v>1.494600093314997</v>
+        <v>1.51705670954691</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.614796320786302</v>
+        <v>1.576348789339009</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1031882926512254</v>
+        <v>0.1033490169030787</v>
       </c>
       <c r="C44">
-        <v>498.7284289665745</v>
+        <v>486.0935100610311</v>
       </c>
       <c r="D44">
-        <v>919.3304289665745</v>
+        <v>917.226510061031</v>
       </c>
       <c r="E44">
-        <v>220.602</v>
+        <v>231.133</v>
       </c>
       <c r="F44">
-        <v>442.302</v>
+        <v>452.833</v>
       </c>
       <c r="G44">
         <v>21.7</v>
@@ -4895,28 +4895,28 @@
         <v>62.75</v>
       </c>
       <c r="M44">
-        <v>39.80718</v>
+        <v>40.75496999999999</v>
       </c>
       <c r="N44">
-        <v>22.94282</v>
+        <v>21.99503000000001</v>
       </c>
       <c r="O44">
-        <v>4.588564000000001</v>
+        <v>4.399006000000002</v>
       </c>
       <c r="P44">
-        <v>18.354256</v>
+        <v>17.59602400000001</v>
       </c>
       <c r="Q44">
-        <v>55.85425600000001</v>
+        <v>55.09602400000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1257729183641818</v>
+        <v>0.126998275268559</v>
       </c>
       <c r="T44">
-        <v>1.51705670954691</v>
+        <v>1.540301277225557</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.576348789339009</v>
+        <v>1.539689515168334</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1033490169030787</v>
+        <v>0.1035097411549319</v>
       </c>
       <c r="C45">
-        <v>486.0935100610311</v>
+        <v>473.4681989474505</v>
       </c>
       <c r="D45">
-        <v>917.226510061031</v>
+        <v>915.1321989474504</v>
       </c>
       <c r="E45">
-        <v>231.133</v>
+        <v>241.664</v>
       </c>
       <c r="F45">
-        <v>452.833</v>
+        <v>463.364</v>
       </c>
       <c r="G45">
         <v>21.7</v>
@@ -4977,28 +4977,28 @@
         <v>62.75</v>
       </c>
       <c r="M45">
-        <v>40.75496999999999</v>
+        <v>41.70276</v>
       </c>
       <c r="N45">
-        <v>21.99503000000001</v>
+        <v>21.04724</v>
       </c>
       <c r="O45">
-        <v>4.399006000000002</v>
+        <v>4.209448000000001</v>
       </c>
       <c r="P45">
-        <v>17.59602400000001</v>
+        <v>16.837792</v>
       </c>
       <c r="Q45">
-        <v>55.09602400000001</v>
+        <v>54.337792</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.126998275268559</v>
+        <v>0.1282673949195212</v>
       </c>
       <c r="T45">
-        <v>1.540301277225557</v>
+        <v>1.564376008035585</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.539689515168334</v>
+        <v>1.504696571641781</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1035097411549319</v>
+        <v>0.1258599039748525</v>
       </c>
       <c r="C46">
-        <v>473.4681989474505</v>
+        <v>242.3947288813388</v>
       </c>
       <c r="D46">
-        <v>915.1321989474504</v>
+        <v>694.5897288813387</v>
       </c>
       <c r="E46">
-        <v>241.664</v>
+        <v>252.195</v>
       </c>
       <c r="F46">
-        <v>463.364</v>
+        <v>473.895</v>
       </c>
       <c r="G46">
         <v>21.7</v>
@@ -5059,45 +5059,45 @@
         <v>62.75</v>
       </c>
       <c r="M46">
-        <v>41.70276</v>
+        <v>69.567786</v>
       </c>
       <c r="N46">
-        <v>21.04724</v>
+        <v>-6.817785999999998</v>
       </c>
       <c r="O46">
-        <v>4.209448000000001</v>
+        <v>-1.3635572</v>
       </c>
       <c r="P46">
-        <v>16.837792</v>
+        <v>-5.454228799999998</v>
       </c>
       <c r="Q46">
-        <v>54.337792</v>
+        <v>32.0457712</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1282673949195212</v>
+        <v>0.1303947287677371</v>
       </c>
       <c r="T46">
-        <v>1.564376008035585</v>
+        <v>1.604730745037749</v>
       </c>
       <c r="U46">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V46">
-        <v>0.2</v>
+        <v>0.1803995889706768</v>
       </c>
       <c r="W46">
-        <v>0.07199999999999999</v>
+        <v>0.1203173403391047</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y46">
-        <v>1.504696571641781</v>
+        <v>0.9019979448533837</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1258599039748525</v>
+        <v>0.1268699039748525</v>
       </c>
       <c r="C47">
-        <v>242.3947288813388</v>
+        <v>224.3807708627194</v>
       </c>
       <c r="D47">
-        <v>694.5897288813387</v>
+        <v>687.1067708627194</v>
       </c>
       <c r="E47">
-        <v>252.195</v>
+        <v>262.726</v>
       </c>
       <c r="F47">
-        <v>473.895</v>
+        <v>484.426</v>
       </c>
       <c r="G47">
         <v>21.7</v>
@@ -5141,37 +5141,37 @@
         <v>62.75</v>
       </c>
       <c r="M47">
-        <v>69.567786</v>
+        <v>71.1137368</v>
       </c>
       <c r="N47">
-        <v>-6.817785999999998</v>
+        <v>-8.363736799999998</v>
       </c>
       <c r="O47">
-        <v>-1.3635572</v>
+        <v>-1.67274736</v>
       </c>
       <c r="P47">
-        <v>-5.454228799999998</v>
+        <v>-6.690989439999998</v>
       </c>
       <c r="Q47">
-        <v>32.0457712</v>
+        <v>30.80901056</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1303947287677371</v>
+        <v>0.1319612978189915</v>
       </c>
       <c r="T47">
-        <v>1.604730745037749</v>
+        <v>1.634447981056967</v>
       </c>
       <c r="U47">
         <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.1803995889706768</v>
+        <v>0.176477858775662</v>
       </c>
       <c r="W47">
-        <v>0.1203173403391047</v>
+        <v>0.1208930503317328</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.9019979448533837</v>
+        <v>0.8823892938783102</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1268699039748525</v>
+        <v>0.1278799039748525</v>
       </c>
       <c r="C48">
-        <v>224.3807708627194</v>
+        <v>206.5263252756564</v>
       </c>
       <c r="D48">
-        <v>687.1067708627194</v>
+        <v>679.7833252756564</v>
       </c>
       <c r="E48">
-        <v>262.726</v>
+        <v>273.257</v>
       </c>
       <c r="F48">
-        <v>484.426</v>
+        <v>494.957</v>
       </c>
       <c r="G48">
         <v>21.7</v>
@@ -5223,37 +5223,37 @@
         <v>62.75</v>
       </c>
       <c r="M48">
-        <v>71.1137368</v>
+        <v>72.65968760000001</v>
       </c>
       <c r="N48">
-        <v>-8.363736799999998</v>
+        <v>-9.909687600000012</v>
       </c>
       <c r="O48">
-        <v>-1.67274736</v>
+        <v>-1.981937520000002</v>
       </c>
       <c r="P48">
-        <v>-6.690989439999998</v>
+        <v>-7.92775008000001</v>
       </c>
       <c r="Q48">
-        <v>30.80901056</v>
+        <v>29.57224991999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1319612978189915</v>
+        <v>0.1335869826835007</v>
       </c>
       <c r="T48">
-        <v>1.634447981056967</v>
+        <v>1.665286622208985</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.176477858775662</v>
+        <v>0.1727230107166054</v>
       </c>
       <c r="W48">
-        <v>0.1208930503317328</v>
+        <v>0.1214442620268023</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.8823892938783102</v>
+        <v>0.8636150535830268</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1278799039748525</v>
+        <v>0.1288899039748525</v>
       </c>
       <c r="C49">
-        <v>206.5263252756564</v>
+        <v>188.8263454765046</v>
       </c>
       <c r="D49">
-        <v>679.7833252756564</v>
+        <v>672.6143454765046</v>
       </c>
       <c r="E49">
-        <v>273.257</v>
+        <v>283.788</v>
       </c>
       <c r="F49">
-        <v>494.957</v>
+        <v>505.488</v>
       </c>
       <c r="G49">
         <v>21.7</v>
@@ -5305,37 +5305,37 @@
         <v>62.75</v>
       </c>
       <c r="M49">
-        <v>72.65968760000001</v>
+        <v>74.20563840000001</v>
       </c>
       <c r="N49">
-        <v>-9.909687600000012</v>
+        <v>-11.45563840000001</v>
       </c>
       <c r="O49">
-        <v>-1.981937520000002</v>
+        <v>-2.291127680000002</v>
       </c>
       <c r="P49">
-        <v>-7.92775008000001</v>
+        <v>-9.16451072000001</v>
       </c>
       <c r="Q49">
-        <v>29.57224991999999</v>
+        <v>28.33548927999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1335869826835007</v>
+        <v>0.1352751938889527</v>
       </c>
       <c r="T49">
-        <v>1.665286622208985</v>
+        <v>1.697311364943774</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.1727230107166054</v>
+        <v>0.1691246146600094</v>
       </c>
       <c r="W49">
-        <v>0.1214442620268023</v>
+        <v>0.1219725065679106</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8636150535830268</v>
+        <v>0.8456230733000472</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1288899039748525</v>
+        <v>0.1298999039748525</v>
       </c>
       <c r="C50">
-        <v>188.8263454765047</v>
+        <v>171.2759954871112</v>
       </c>
       <c r="D50">
-        <v>672.6143454765046</v>
+        <v>665.5949954871111</v>
       </c>
       <c r="E50">
-        <v>283.788</v>
+        <v>294.3189999999999</v>
       </c>
       <c r="F50">
-        <v>505.4879999999999</v>
+        <v>516.0189999999999</v>
       </c>
       <c r="G50">
         <v>21.7</v>
@@ -5387,37 +5387,37 @@
         <v>62.75</v>
       </c>
       <c r="M50">
-        <v>74.2056384</v>
+        <v>75.7515892</v>
       </c>
       <c r="N50">
-        <v>-11.4556384</v>
+        <v>-13.0015892</v>
       </c>
       <c r="O50">
-        <v>-2.29112768</v>
+        <v>-2.60031784</v>
       </c>
       <c r="P50">
-        <v>-9.164510719999999</v>
+        <v>-10.40127136</v>
       </c>
       <c r="Q50">
-        <v>28.33548928</v>
+        <v>27.09872864</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1352751938889527</v>
+        <v>0.1370296094554027</v>
       </c>
       <c r="T50">
-        <v>1.697311364943773</v>
+        <v>1.730591979942671</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.1691246146600095</v>
+        <v>0.165673091911846</v>
       </c>
       <c r="W50">
-        <v>0.1219725065679106</v>
+        <v>0.122479190107341</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8456230733000473</v>
+        <v>0.82836545955923</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1298999039748525</v>
+        <v>0.1309099039748525</v>
       </c>
       <c r="C51">
-        <v>171.2759954871112</v>
+        <v>153.8706391159044</v>
       </c>
       <c r="D51">
-        <v>665.5949954871111</v>
+        <v>658.7206391159043</v>
       </c>
       <c r="E51">
-        <v>294.3189999999999</v>
+        <v>304.85</v>
       </c>
       <c r="F51">
-        <v>516.0189999999999</v>
+        <v>526.55</v>
       </c>
       <c r="G51">
         <v>21.7</v>
@@ -5469,37 +5469,37 @@
         <v>62.75</v>
       </c>
       <c r="M51">
-        <v>75.7515892</v>
+        <v>77.29754</v>
       </c>
       <c r="N51">
-        <v>-13.0015892</v>
+        <v>-14.54754</v>
       </c>
       <c r="O51">
-        <v>-2.60031784</v>
+        <v>-2.909508</v>
       </c>
       <c r="P51">
-        <v>-10.40127136</v>
+        <v>-11.638032</v>
       </c>
       <c r="Q51">
-        <v>27.09872864</v>
+        <v>25.861968</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1370296094554027</v>
+        <v>0.1388542016445108</v>
       </c>
       <c r="T51">
-        <v>1.730591979942671</v>
+        <v>1.765203819541524</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.165673091911846</v>
+        <v>0.1623596300736091</v>
       </c>
       <c r="W51">
-        <v>0.122479190107341</v>
+        <v>0.1229656063051942</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.82836545955923</v>
+        <v>0.8117981503680454</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1309099039748525</v>
+        <v>0.1605653908053369</v>
       </c>
       <c r="C52">
-        <v>153.8706391159044</v>
+        <v>-9.937746113967478</v>
       </c>
       <c r="D52">
-        <v>658.7206391159043</v>
+        <v>505.4432538860325</v>
       </c>
       <c r="E52">
-        <v>304.85</v>
+        <v>315.381</v>
       </c>
       <c r="F52">
-        <v>526.55</v>
+        <v>537.081</v>
       </c>
       <c r="G52">
         <v>21.7</v>
@@ -5551,45 +5551,45 @@
         <v>62.75</v>
       </c>
       <c r="M52">
-        <v>77.29754</v>
+        <v>107.8458648</v>
       </c>
       <c r="N52">
-        <v>-14.54754</v>
+        <v>-45.0958648</v>
       </c>
       <c r="O52">
-        <v>-2.909508</v>
+        <v>-9.019172960000001</v>
       </c>
       <c r="P52">
-        <v>-11.638032</v>
+        <v>-36.07669184</v>
       </c>
       <c r="Q52">
-        <v>25.861968</v>
+        <v>1.423308159999998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1388542016445108</v>
+        <v>0.143009362556612</v>
       </c>
       <c r="T52">
-        <v>1.765203819541524</v>
+        <v>1.844025686617134</v>
       </c>
       <c r="U52">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V52">
-        <v>0.1623596300736091</v>
+        <v>0.1163697840735383</v>
       </c>
       <c r="W52">
-        <v>0.1229656063051942</v>
+        <v>0.1774329473580335</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y52">
-        <v>0.8117981503680454</v>
+        <v>0.5818489203676913</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1605653908053369</v>
+        <v>0.1621153908053369</v>
       </c>
       <c r="C53">
-        <v>-9.937746113967478</v>
+        <v>-26.54206167447057</v>
       </c>
       <c r="D53">
-        <v>505.4432538860325</v>
+        <v>499.3699383255293</v>
       </c>
       <c r="E53">
-        <v>315.381</v>
+        <v>325.912</v>
       </c>
       <c r="F53">
-        <v>537.081</v>
+        <v>547.612</v>
       </c>
       <c r="G53">
         <v>21.7</v>
@@ -5633,37 +5633,37 @@
         <v>62.75</v>
       </c>
       <c r="M53">
-        <v>107.8458648</v>
+        <v>109.9604896</v>
       </c>
       <c r="N53">
-        <v>-45.0958648</v>
+        <v>-47.2104896</v>
       </c>
       <c r="O53">
-        <v>-9.019172960000001</v>
+        <v>-9.44209792</v>
       </c>
       <c r="P53">
-        <v>-36.07669184</v>
+        <v>-37.76839168</v>
       </c>
       <c r="Q53">
-        <v>1.423308159999998</v>
+        <v>-0.2683916800000006</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.143009362556612</v>
+        <v>0.1450345576098747</v>
       </c>
       <c r="T53">
-        <v>1.844025686617134</v>
+        <v>1.882442888421658</v>
       </c>
       <c r="U53">
         <v>0.2008</v>
       </c>
       <c r="V53">
-        <v>0.1163697840735383</v>
+        <v>0.1141319036105856</v>
       </c>
       <c r="W53">
-        <v>0.1774329473580335</v>
+        <v>0.1778823137549944</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.5818489203676913</v>
+        <v>0.5706595180529279</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1621153908053369</v>
+        <v>0.163665390805337</v>
       </c>
       <c r="C54">
-        <v>-26.54206167447057</v>
+        <v>-43.00215839984492</v>
       </c>
       <c r="D54">
-        <v>499.3699383255293</v>
+        <v>493.4408416001551</v>
       </c>
       <c r="E54">
-        <v>325.912</v>
+        <v>336.443</v>
       </c>
       <c r="F54">
-        <v>547.612</v>
+        <v>558.143</v>
       </c>
       <c r="G54">
         <v>21.7</v>
@@ -5715,37 +5715,37 @@
         <v>62.75</v>
       </c>
       <c r="M54">
-        <v>109.9604896</v>
+        <v>112.0751144</v>
       </c>
       <c r="N54">
-        <v>-47.2104896</v>
+        <v>-49.3251144</v>
       </c>
       <c r="O54">
-        <v>-9.44209792</v>
+        <v>-9.865022880000001</v>
       </c>
       <c r="P54">
-        <v>-37.76839168</v>
+        <v>-39.46009152000001</v>
       </c>
       <c r="Q54">
-        <v>-0.2683916800000006</v>
+        <v>-1.960091520000006</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1450345576098747</v>
+        <v>0.1471459311760423</v>
       </c>
       <c r="T54">
-        <v>1.882442888421658</v>
+        <v>1.922494864771055</v>
       </c>
       <c r="U54">
         <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.1141319036105856</v>
+        <v>0.1119784714669897</v>
       </c>
       <c r="W54">
-        <v>0.1778823137549944</v>
+        <v>0.1783147229294285</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.5706595180529279</v>
+        <v>0.5598923573349481</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.163665390805337</v>
+        <v>0.165215390805337</v>
       </c>
       <c r="C55">
-        <v>-43.00215839984492</v>
+        <v>-59.32311301118204</v>
       </c>
       <c r="D55">
-        <v>493.4408416001551</v>
+        <v>487.6508869888179</v>
       </c>
       <c r="E55">
-        <v>336.443</v>
+        <v>346.974</v>
       </c>
       <c r="F55">
-        <v>558.143</v>
+        <v>568.674</v>
       </c>
       <c r="G55">
         <v>21.7</v>
@@ -5797,37 +5797,37 @@
         <v>62.75</v>
       </c>
       <c r="M55">
-        <v>112.0751144</v>
+        <v>114.1897392</v>
       </c>
       <c r="N55">
-        <v>-49.3251144</v>
+        <v>-51.43973920000001</v>
       </c>
       <c r="O55">
-        <v>-9.865022880000001</v>
+        <v>-10.28794784</v>
       </c>
       <c r="P55">
-        <v>-39.46009152000001</v>
+        <v>-41.15179136</v>
       </c>
       <c r="Q55">
-        <v>-1.960091520000006</v>
+        <v>-3.651791360000004</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1471459311760423</v>
+        <v>0.1493491035929127</v>
       </c>
       <c r="T55">
-        <v>1.922494864771055</v>
+        <v>1.964288231396513</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.1119784714669897</v>
+        <v>0.1099047960694528</v>
       </c>
       <c r="W55">
-        <v>0.1783147229294285</v>
+        <v>0.1787311169492539</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5598923573349481</v>
+        <v>0.549523980347264</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.165215390805337</v>
+        <v>0.166765390805337</v>
       </c>
       <c r="C56">
-        <v>-59.32311301118204</v>
+        <v>-75.50976671538086</v>
       </c>
       <c r="D56">
-        <v>487.6508869888179</v>
+        <v>481.9952332846192</v>
       </c>
       <c r="E56">
-        <v>346.974</v>
+        <v>357.5050000000001</v>
       </c>
       <c r="F56">
-        <v>568.674</v>
+        <v>579.205</v>
       </c>
       <c r="G56">
         <v>21.7</v>
@@ -5879,37 +5879,37 @@
         <v>62.75</v>
       </c>
       <c r="M56">
-        <v>114.1897392</v>
+        <v>116.304364</v>
       </c>
       <c r="N56">
-        <v>-51.43973920000001</v>
+        <v>-53.55436400000001</v>
       </c>
       <c r="O56">
-        <v>-10.28794784</v>
+        <v>-10.7108728</v>
       </c>
       <c r="P56">
-        <v>-41.15179136</v>
+        <v>-42.8434912</v>
       </c>
       <c r="Q56">
-        <v>-3.651791360000004</v>
+        <v>-5.343491200000003</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1493491035929127</v>
+        <v>0.1516501947838664</v>
       </c>
       <c r="T56">
-        <v>1.964288231396513</v>
+        <v>2.007939080983102</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1099047960694528</v>
+        <v>0.1079065270500082</v>
       </c>
       <c r="W56">
-        <v>0.1787311169492539</v>
+        <v>0.1791323693683584</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.549523980347264</v>
+        <v>0.5395326352500409</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.166765390805337</v>
+        <v>0.1683153908053369</v>
       </c>
       <c r="C57">
-        <v>-75.50976671538086</v>
+        <v>-91.56673870574343</v>
       </c>
       <c r="D57">
-        <v>481.9952332846192</v>
+        <v>476.4692612942566</v>
       </c>
       <c r="E57">
-        <v>357.5050000000001</v>
+        <v>368.036</v>
       </c>
       <c r="F57">
-        <v>579.205</v>
+        <v>589.736</v>
       </c>
       <c r="G57">
         <v>21.7</v>
@@ -5961,37 +5961,37 @@
         <v>62.75</v>
       </c>
       <c r="M57">
-        <v>116.304364</v>
+        <v>118.4189888</v>
       </c>
       <c r="N57">
-        <v>-53.55436400000001</v>
+        <v>-55.66898880000001</v>
       </c>
       <c r="O57">
-        <v>-10.7108728</v>
+        <v>-11.13379776</v>
       </c>
       <c r="P57">
-        <v>-42.8434912</v>
+        <v>-44.53519104000001</v>
       </c>
       <c r="Q57">
-        <v>-5.343491200000003</v>
+        <v>-7.035191040000008</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1516501947838664</v>
+        <v>0.1540558810289542</v>
       </c>
       <c r="T57">
-        <v>2.007939080983102</v>
+        <v>2.053574060096354</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1079065270500082</v>
+        <v>0.1059796247812581</v>
       </c>
       <c r="W57">
-        <v>0.1791323693683584</v>
+        <v>0.1795192913439234</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5395326352500409</v>
+        <v>0.5298981239062902</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1683153908053369</v>
+        <v>0.169865390805337</v>
       </c>
       <c r="C58">
-        <v>-91.56673870574343</v>
+        <v>-107.4984387444131</v>
       </c>
       <c r="D58">
-        <v>476.4692612942566</v>
+        <v>471.0685612555869</v>
       </c>
       <c r="E58">
-        <v>368.036</v>
+        <v>378.5670000000001</v>
       </c>
       <c r="F58">
-        <v>589.736</v>
+        <v>600.2670000000001</v>
       </c>
       <c r="G58">
         <v>21.7</v>
@@ -6043,37 +6043,37 @@
         <v>62.75</v>
       </c>
       <c r="M58">
-        <v>118.4189888</v>
+        <v>120.5336136</v>
       </c>
       <c r="N58">
-        <v>-55.66898880000001</v>
+        <v>-57.78361360000001</v>
       </c>
       <c r="O58">
-        <v>-11.13379776</v>
+        <v>-11.55672272</v>
       </c>
       <c r="P58">
-        <v>-44.53519104000001</v>
+        <v>-46.22689088000001</v>
       </c>
       <c r="Q58">
-        <v>-7.035191040000008</v>
+        <v>-8.726890880000006</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1540558810289542</v>
+        <v>0.1565734596575346</v>
       </c>
       <c r="T58">
-        <v>2.053574060096354</v>
+        <v>2.101331596377665</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1059796247812581</v>
+        <v>0.104120333118429</v>
       </c>
       <c r="W58">
-        <v>0.1795192913439234</v>
+        <v>0.1798926371098195</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5298981239062902</v>
+        <v>0.5206016655921448</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.169865390805337</v>
+        <v>0.171415390805337</v>
       </c>
       <c r="C59">
-        <v>-107.4984387444131</v>
+        <v>-123.3090788986815</v>
       </c>
       <c r="D59">
-        <v>471.0685612555869</v>
+        <v>465.7889211013185</v>
       </c>
       <c r="E59">
-        <v>378.5670000000001</v>
+        <v>389.098</v>
       </c>
       <c r="F59">
-        <v>600.2670000000001</v>
+        <v>610.798</v>
       </c>
       <c r="G59">
         <v>21.7</v>
@@ -6125,37 +6125,37 @@
         <v>62.75</v>
       </c>
       <c r="M59">
-        <v>120.5336136</v>
+        <v>122.6482384</v>
       </c>
       <c r="N59">
-        <v>-57.78361360000001</v>
+        <v>-59.89823840000001</v>
       </c>
       <c r="O59">
-        <v>-11.55672272</v>
+        <v>-11.97964768</v>
       </c>
       <c r="P59">
-        <v>-46.22689088000001</v>
+        <v>-47.91859072000001</v>
       </c>
       <c r="Q59">
-        <v>-8.726890880000006</v>
+        <v>-10.41859072000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1565734596575346</v>
+        <v>0.1592109229827139</v>
       </c>
       <c r="T59">
-        <v>2.101331596377665</v>
+        <v>2.151363301053324</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.104120333118429</v>
+        <v>0.1023251549612147</v>
       </c>
       <c r="W59">
-        <v>0.1798926371098195</v>
+        <v>0.1802531088837881</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5206016655921448</v>
+        <v>0.5116257748060733</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1714153908053369</v>
+        <v>0.172965390805337</v>
       </c>
       <c r="C60">
-        <v>-123.3090788986813</v>
+        <v>-139.0026844968161</v>
       </c>
       <c r="D60">
-        <v>465.7889211013186</v>
+        <v>460.6263155031839</v>
       </c>
       <c r="E60">
-        <v>389.0979999999999</v>
+        <v>399.629</v>
       </c>
       <c r="F60">
-        <v>610.7979999999999</v>
+        <v>621.329</v>
       </c>
       <c r="G60">
         <v>21.7</v>
@@ -6207,37 +6207,37 @@
         <v>62.75</v>
       </c>
       <c r="M60">
-        <v>122.6482384</v>
+        <v>124.7628632</v>
       </c>
       <c r="N60">
-        <v>-59.89823839999998</v>
+        <v>-62.0128632</v>
       </c>
       <c r="O60">
-        <v>-11.97964768</v>
+        <v>-12.40257264</v>
       </c>
       <c r="P60">
-        <v>-47.91859071999998</v>
+        <v>-49.61029056</v>
       </c>
       <c r="Q60">
-        <v>-10.41859071999998</v>
+        <v>-12.11029056</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1592109229827139</v>
+        <v>0.161977043055463</v>
       </c>
       <c r="T60">
-        <v>2.151363301053323</v>
+        <v>2.20383557668877</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1023251549612147</v>
+        <v>0.1005908303008551</v>
       </c>
       <c r="W60">
-        <v>0.1802531088837881</v>
+        <v>0.1806013612755883</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.5116257748060735</v>
+        <v>0.5029541515042755</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.172965390805337</v>
+        <v>0.1959614680942375</v>
       </c>
       <c r="C61">
-        <v>-139.0026844968161</v>
+        <v>-214.5817338433326</v>
       </c>
       <c r="D61">
-        <v>460.6263155031839</v>
+        <v>395.5782661566673</v>
       </c>
       <c r="E61">
-        <v>399.629</v>
+        <v>410.1599999999999</v>
       </c>
       <c r="F61">
-        <v>621.329</v>
+        <v>631.8599999999999</v>
       </c>
       <c r="G61">
         <v>21.7</v>
@@ -6289,45 +6289,45 @@
         <v>62.75</v>
       </c>
       <c r="M61">
-        <v>124.7628632</v>
+        <v>148.992588</v>
       </c>
       <c r="N61">
-        <v>-62.0128632</v>
+        <v>-86.24258799999998</v>
       </c>
       <c r="O61">
-        <v>-12.40257264</v>
+        <v>-17.2485176</v>
       </c>
       <c r="P61">
-        <v>-49.61029056</v>
+        <v>-68.99407039999998</v>
       </c>
       <c r="Q61">
-        <v>-12.11029056</v>
+        <v>-31.49407039999998</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.161977043055463</v>
+        <v>0.1659966623541011</v>
       </c>
       <c r="T61">
-        <v>2.20383557668877</v>
+        <v>2.28008626944271</v>
       </c>
       <c r="U61">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.1005908303008551</v>
+        <v>0.08423237805628292</v>
       </c>
       <c r="W61">
-        <v>0.1806013612755883</v>
+        <v>0.2159380052543285</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y61">
-        <v>0.5029541515042755</v>
+        <v>0.4211618902814146</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1959614680942375</v>
+        <v>0.1978614680942375</v>
       </c>
       <c r="C62">
-        <v>-214.5817338433326</v>
+        <v>-229.6749925668479</v>
       </c>
       <c r="D62">
-        <v>395.5782661566673</v>
+        <v>391.016007433152</v>
       </c>
       <c r="E62">
-        <v>410.1599999999999</v>
+        <v>420.691</v>
       </c>
       <c r="F62">
-        <v>631.8599999999999</v>
+        <v>642.391</v>
       </c>
       <c r="G62">
         <v>21.7</v>
@@ -6371,37 +6371,37 @@
         <v>62.75</v>
       </c>
       <c r="M62">
-        <v>148.992588</v>
+        <v>151.4757978</v>
       </c>
       <c r="N62">
-        <v>-86.24258799999998</v>
+        <v>-88.72579780000001</v>
       </c>
       <c r="O62">
-        <v>-17.2485176</v>
+        <v>-17.74515956</v>
       </c>
       <c r="P62">
-        <v>-68.99407039999998</v>
+        <v>-70.98063824</v>
       </c>
       <c r="Q62">
-        <v>-31.49407039999998</v>
+        <v>-33.48063824</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1659966623541011</v>
+        <v>0.1690786280554883</v>
       </c>
       <c r="T62">
-        <v>2.28008626944271</v>
+        <v>2.338550019941241</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.08423237805628292</v>
+        <v>0.08285151939962254</v>
       </c>
       <c r="W62">
-        <v>0.2159380052543285</v>
+        <v>0.216263611725569</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.4211618902814146</v>
+        <v>0.4142575969981126</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1978614680942375</v>
+        <v>0.1997614680942376</v>
       </c>
       <c r="C63">
-        <v>-229.6749925668479</v>
+        <v>-244.6642168156419</v>
       </c>
       <c r="D63">
-        <v>391.016007433152</v>
+        <v>386.557783184358</v>
       </c>
       <c r="E63">
-        <v>420.691</v>
+        <v>431.2219999999999</v>
       </c>
       <c r="F63">
-        <v>642.391</v>
+        <v>652.9219999999999</v>
       </c>
       <c r="G63">
         <v>21.7</v>
@@ -6453,37 +6453,37 @@
         <v>62.75</v>
       </c>
       <c r="M63">
-        <v>151.4757978</v>
+        <v>153.9590076</v>
       </c>
       <c r="N63">
-        <v>-88.72579780000001</v>
+        <v>-91.20900759999998</v>
       </c>
       <c r="O63">
-        <v>-17.74515956</v>
+        <v>-18.24180152</v>
       </c>
       <c r="P63">
-        <v>-70.98063824</v>
+        <v>-72.96720607999998</v>
       </c>
       <c r="Q63">
-        <v>-33.48063824</v>
+        <v>-35.46720607999998</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1690786280554883</v>
+        <v>0.1723228024780012</v>
       </c>
       <c r="T63">
-        <v>2.338550019941241</v>
+        <v>2.400090809939695</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.08285151939962254</v>
+        <v>0.08151520457059638</v>
       </c>
       <c r="W63">
-        <v>0.216263611725569</v>
+        <v>0.2165787147622534</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.4142575969981126</v>
+        <v>0.4075760228529819</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1997614680942376</v>
+        <v>0.2016614680942376</v>
       </c>
       <c r="C64">
-        <v>-244.6642168156419</v>
+        <v>-259.5529249657359</v>
       </c>
       <c r="D64">
-        <v>386.557783184358</v>
+        <v>382.2000750342641</v>
       </c>
       <c r="E64">
-        <v>431.2219999999999</v>
+        <v>441.753</v>
       </c>
       <c r="F64">
-        <v>652.9219999999999</v>
+        <v>663.453</v>
       </c>
       <c r="G64">
         <v>21.7</v>
@@ -6535,37 +6535,37 @@
         <v>62.75</v>
       </c>
       <c r="M64">
-        <v>153.9590076</v>
+        <v>156.4422174</v>
       </c>
       <c r="N64">
-        <v>-91.20900759999998</v>
+        <v>-93.6922174</v>
       </c>
       <c r="O64">
-        <v>-18.24180152</v>
+        <v>-18.73844348</v>
       </c>
       <c r="P64">
-        <v>-72.96720607999998</v>
+        <v>-74.95377392</v>
       </c>
       <c r="Q64">
-        <v>-35.46720607999998</v>
+        <v>-37.45377392</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1723228024780012</v>
+        <v>0.1757423376801093</v>
       </c>
       <c r="T64">
-        <v>2.400090809939695</v>
+        <v>2.464958129127254</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.08151520457059638</v>
+        <v>0.08022131243455516</v>
       </c>
       <c r="W64">
-        <v>0.2165787147622534</v>
+        <v>0.2168838145279319</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4075760228529819</v>
+        <v>0.4011065621727757</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2016614680942376</v>
+        <v>0.2035614680942376</v>
       </c>
       <c r="C65">
-        <v>-259.5529249657359</v>
+        <v>-274.3444785095666</v>
       </c>
       <c r="D65">
-        <v>382.2000750342641</v>
+        <v>377.9395214904334</v>
       </c>
       <c r="E65">
-        <v>441.753</v>
+        <v>452.2839999999999</v>
       </c>
       <c r="F65">
-        <v>663.453</v>
+        <v>673.9839999999999</v>
       </c>
       <c r="G65">
         <v>21.7</v>
@@ -6617,37 +6617,37 @@
         <v>62.75</v>
       </c>
       <c r="M65">
-        <v>156.4422174</v>
+        <v>158.9254272</v>
       </c>
       <c r="N65">
-        <v>-93.6922174</v>
+        <v>-96.1754272</v>
       </c>
       <c r="O65">
-        <v>-18.73844348</v>
+        <v>-19.23508544</v>
       </c>
       <c r="P65">
-        <v>-74.95377392</v>
+        <v>-76.94034176</v>
       </c>
       <c r="Q65">
-        <v>-37.45377392</v>
+        <v>-39.44034176</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1757423376801093</v>
+        <v>0.1793518470601124</v>
       </c>
       <c r="T65">
-        <v>2.464958129127254</v>
+        <v>2.533429188269678</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.08022131243455516</v>
+        <v>0.07896785442776523</v>
       </c>
       <c r="W65">
-        <v>0.2168838145279319</v>
+        <v>0.217179379925933</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4011065621727757</v>
+        <v>0.3948392721388261</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2035614680942376</v>
+        <v>0.2054614680942375</v>
       </c>
       <c r="C66">
-        <v>-274.3444785095666</v>
+        <v>-289.0420907038392</v>
       </c>
       <c r="D66">
-        <v>377.9395214904334</v>
+        <v>373.7729092961608</v>
       </c>
       <c r="E66">
-        <v>452.2839999999999</v>
+        <v>462.815</v>
       </c>
       <c r="F66">
-        <v>673.9839999999999</v>
+        <v>684.515</v>
       </c>
       <c r="G66">
         <v>21.7</v>
@@ -6699,37 +6699,37 @@
         <v>62.75</v>
       </c>
       <c r="M66">
-        <v>158.9254272</v>
+        <v>161.408637</v>
       </c>
       <c r="N66">
-        <v>-96.1754272</v>
+        <v>-98.658637</v>
       </c>
       <c r="O66">
-        <v>-19.23508544</v>
+        <v>-19.7317274</v>
       </c>
       <c r="P66">
-        <v>-76.94034176</v>
+        <v>-78.9269096</v>
       </c>
       <c r="Q66">
-        <v>-39.44034176</v>
+        <v>-41.4269096</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1793518470601124</v>
+        <v>0.1831676141189728</v>
       </c>
       <c r="T66">
-        <v>2.533429188269678</v>
+        <v>2.605812879363098</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.07896785442776523</v>
+        <v>0.07775296435964577</v>
       </c>
       <c r="W66">
-        <v>0.217179379925933</v>
+        <v>0.2174658510039955</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.3948392721388261</v>
+        <v>0.3887648217982288</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2054614680942375</v>
+        <v>0.2073614680942376</v>
       </c>
       <c r="C67">
-        <v>-289.0420907038392</v>
+        <v>-303.6488346515853</v>
       </c>
       <c r="D67">
-        <v>373.7729092961608</v>
+        <v>369.6971653484146</v>
       </c>
       <c r="E67">
-        <v>462.815</v>
+        <v>473.3459999999999</v>
       </c>
       <c r="F67">
-        <v>684.515</v>
+        <v>695.0459999999999</v>
       </c>
       <c r="G67">
         <v>21.7</v>
@@ -6781,37 +6781,37 @@
         <v>62.75</v>
       </c>
       <c r="M67">
-        <v>161.408637</v>
+        <v>163.8918468</v>
       </c>
       <c r="N67">
-        <v>-98.658637</v>
+        <v>-101.1418468</v>
       </c>
       <c r="O67">
-        <v>-19.7317274</v>
+        <v>-20.22836936</v>
       </c>
       <c r="P67">
-        <v>-78.9269096</v>
+        <v>-80.91347743999999</v>
       </c>
       <c r="Q67">
-        <v>-41.4269096</v>
+        <v>-43.41347743999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1831676141189728</v>
+        <v>0.1872078380636484</v>
       </c>
       <c r="T67">
-        <v>2.605812879363098</v>
+        <v>2.682454434638483</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.07775296435964577</v>
+        <v>0.07657488914207539</v>
       </c>
       <c r="W67">
-        <v>0.2174658510039955</v>
+        <v>0.2177436411402986</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3887648217982288</v>
+        <v>0.3828744457103769</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2073614680942376</v>
+        <v>0.2092614680942376</v>
       </c>
       <c r="C68">
-        <v>-303.6488346515853</v>
+        <v>-318.1676508611488</v>
       </c>
       <c r="D68">
-        <v>369.6971653484146</v>
+        <v>365.7093491388512</v>
       </c>
       <c r="E68">
-        <v>473.3459999999999</v>
+        <v>483.877</v>
       </c>
       <c r="F68">
-        <v>695.0459999999999</v>
+        <v>705.577</v>
       </c>
       <c r="G68">
         <v>21.7</v>
@@ -6863,37 +6863,37 @@
         <v>62.75</v>
       </c>
       <c r="M68">
-        <v>163.8918468</v>
+        <v>166.3750566</v>
       </c>
       <c r="N68">
-        <v>-101.1418468</v>
+        <v>-103.6250566</v>
       </c>
       <c r="O68">
-        <v>-20.22836936</v>
+        <v>-20.72501132</v>
       </c>
       <c r="P68">
-        <v>-80.91347743999999</v>
+        <v>-82.90004528</v>
       </c>
       <c r="Q68">
-        <v>-43.41347743999999</v>
+        <v>-45.40004528</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1872078380636484</v>
+        <v>0.1914929240655772</v>
       </c>
       <c r="T68">
-        <v>2.682454434638483</v>
+        <v>2.763740932657831</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.07657488914207539</v>
+        <v>0.07543198034891008</v>
       </c>
       <c r="W68">
-        <v>0.2177436411402986</v>
+        <v>0.218013139033727</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3828744457103769</v>
+        <v>0.3771599017445504</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2092614680942376</v>
+        <v>0.2111614680942376</v>
       </c>
       <c r="C69">
-        <v>-318.1676508611488</v>
+        <v>-332.6013543211713</v>
       </c>
       <c r="D69">
-        <v>365.7093491388512</v>
+        <v>361.8066456788287</v>
       </c>
       <c r="E69">
-        <v>483.877</v>
+        <v>494.408</v>
       </c>
       <c r="F69">
-        <v>705.577</v>
+        <v>716.1079999999999</v>
       </c>
       <c r="G69">
         <v>21.7</v>
@@ -6945,37 +6945,37 @@
         <v>62.75</v>
       </c>
       <c r="M69">
-        <v>166.3750566</v>
+        <v>168.8582664</v>
       </c>
       <c r="N69">
-        <v>-103.6250566</v>
+        <v>-106.1082664</v>
       </c>
       <c r="O69">
-        <v>-20.72501132</v>
+        <v>-21.22165328</v>
       </c>
       <c r="P69">
-        <v>-82.90004528</v>
+        <v>-84.88661311999999</v>
       </c>
       <c r="Q69">
-        <v>-45.40004528</v>
+        <v>-47.38661311999999</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1914929240655772</v>
+        <v>0.1960458279426265</v>
       </c>
       <c r="T69">
-        <v>2.763740932657831</v>
+        <v>2.850107836803388</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.07543198034891008</v>
+        <v>0.07432268652024963</v>
       </c>
       <c r="W69">
-        <v>0.218013139033727</v>
+        <v>0.2182747105185252</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3771599017445504</v>
+        <v>0.3716134326012481</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2111614680942376</v>
+        <v>0.2130614680942376</v>
       </c>
       <c r="C70">
-        <v>-332.6013543211713</v>
+        <v>-346.9526411273549</v>
       </c>
       <c r="D70">
-        <v>361.8066456788287</v>
+        <v>357.9863588726452</v>
       </c>
       <c r="E70">
-        <v>494.408</v>
+        <v>504.939</v>
       </c>
       <c r="F70">
-        <v>716.1079999999999</v>
+        <v>726.639</v>
       </c>
       <c r="G70">
         <v>21.7</v>
@@ -7027,37 +7027,37 @@
         <v>62.75</v>
       </c>
       <c r="M70">
-        <v>168.8582664</v>
+        <v>171.3414762</v>
       </c>
       <c r="N70">
-        <v>-106.1082664</v>
+        <v>-108.5914762</v>
       </c>
       <c r="O70">
-        <v>-21.22165328</v>
+        <v>-21.71829524</v>
       </c>
       <c r="P70">
-        <v>-84.88661311999999</v>
+        <v>-86.87318096000001</v>
       </c>
       <c r="Q70">
-        <v>-47.38661311999999</v>
+        <v>-49.37318096000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1960458279426265</v>
+        <v>0.2008924675536789</v>
       </c>
       <c r="T70">
-        <v>2.850107836803388</v>
+        <v>2.942046799280917</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.07432268652024963</v>
+        <v>0.07324554613589818</v>
       </c>
       <c r="W70">
-        <v>0.2182747105185252</v>
+        <v>0.2185287002211552</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3716134326012481</v>
+        <v>0.3662277306794909</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2130614680942376</v>
+        <v>0.2149614680942376</v>
       </c>
       <c r="C71">
-        <v>-346.9526411273549</v>
+        <v>-361.2240946937806</v>
       </c>
       <c r="D71">
-        <v>357.9863588726452</v>
+        <v>354.2459053062194</v>
       </c>
       <c r="E71">
-        <v>504.939</v>
+        <v>515.47</v>
       </c>
       <c r="F71">
-        <v>726.639</v>
+        <v>737.17</v>
       </c>
       <c r="G71">
         <v>21.7</v>
@@ -7109,37 +7109,37 @@
         <v>62.75</v>
       </c>
       <c r="M71">
-        <v>171.3414762</v>
+        <v>173.824686</v>
       </c>
       <c r="N71">
-        <v>-108.5914762</v>
+        <v>-111.074686</v>
       </c>
       <c r="O71">
-        <v>-21.71829524</v>
+        <v>-22.2149372</v>
       </c>
       <c r="P71">
-        <v>-86.87318096000001</v>
+        <v>-88.85974879999999</v>
       </c>
       <c r="Q71">
-        <v>-49.37318096000001</v>
+        <v>-51.35974879999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2008924675536789</v>
+        <v>0.2060622164721349</v>
       </c>
       <c r="T71">
-        <v>2.942046799280917</v>
+        <v>3.040115025923614</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.07324554613589818</v>
+        <v>0.07219918119109964</v>
       </c>
       <c r="W71">
-        <v>0.2185287002211552</v>
+        <v>0.2187754330751387</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3662277306794909</v>
+        <v>0.3609959059554982</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2149614680942376</v>
+        <v>0.2168614680942376</v>
       </c>
       <c r="C72">
-        <v>-361.2240946937806</v>
+        <v>-375.4181915788575</v>
       </c>
       <c r="D72">
-        <v>354.2459053062194</v>
+        <v>350.5828084211425</v>
       </c>
       <c r="E72">
-        <v>515.47</v>
+        <v>526.001</v>
       </c>
       <c r="F72">
-        <v>737.17</v>
+        <v>747.701</v>
       </c>
       <c r="G72">
         <v>21.7</v>
@@ -7191,37 +7191,37 @@
         <v>62.75</v>
       </c>
       <c r="M72">
-        <v>173.824686</v>
+        <v>176.3078958</v>
       </c>
       <c r="N72">
-        <v>-111.074686</v>
+        <v>-113.5578958</v>
       </c>
       <c r="O72">
-        <v>-22.2149372</v>
+        <v>-22.71157916</v>
       </c>
       <c r="P72">
-        <v>-88.85974879999999</v>
+        <v>-90.84631664000001</v>
       </c>
       <c r="Q72">
-        <v>-51.35974879999999</v>
+        <v>-53.34631664000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2060622164721349</v>
+        <v>0.2115884997987603</v>
       </c>
       <c r="T72">
-        <v>3.040115025923614</v>
+        <v>3.14494657854167</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.07219918119109964</v>
+        <v>0.07118229131516865</v>
       </c>
       <c r="W72">
-        <v>0.2187754330751387</v>
+        <v>0.2190152157078832</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.3609959059554982</v>
+        <v>0.3559114565758432</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2168614680942376</v>
+        <v>0.2187614680942375</v>
       </c>
       <c r="C73">
-        <v>-375.4181915788574</v>
+        <v>-389.5373069535094</v>
       </c>
       <c r="D73">
-        <v>350.5828084211425</v>
+        <v>346.9946930464905</v>
       </c>
       <c r="E73">
-        <v>526.001</v>
+        <v>536.5319999999999</v>
       </c>
       <c r="F73">
-        <v>747.7009999999999</v>
+        <v>758.2319999999999</v>
       </c>
       <c r="G73">
         <v>21.7</v>
@@ -7273,37 +7273,37 @@
         <v>62.75</v>
       </c>
       <c r="M73">
-        <v>176.3078958</v>
+        <v>178.7911056</v>
       </c>
       <c r="N73">
-        <v>-113.5578958</v>
+        <v>-116.0411056</v>
       </c>
       <c r="O73">
-        <v>-22.71157916</v>
+        <v>-23.20822112</v>
       </c>
       <c r="P73">
-        <v>-90.84631663999998</v>
+        <v>-92.83288447999999</v>
       </c>
       <c r="Q73">
-        <v>-53.34631663999998</v>
+        <v>-55.33288447999999</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2115884997987602</v>
+        <v>0.2175095176487159</v>
       </c>
       <c r="T73">
-        <v>3.144946578541669</v>
+        <v>3.257266099203872</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.07118229131516866</v>
+        <v>0.07019364838023577</v>
       </c>
       <c r="W73">
-        <v>0.2190152157078832</v>
+        <v>0.2192483377119404</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3559114565758433</v>
+        <v>0.3509682419011788</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2187614680942375</v>
+        <v>0.2206614680942375</v>
       </c>
       <c r="C74">
-        <v>-389.5373069535094</v>
+        <v>-403.583719736973</v>
       </c>
       <c r="D74">
-        <v>346.9946930464905</v>
+        <v>343.479280263027</v>
       </c>
       <c r="E74">
-        <v>536.5319999999999</v>
+        <v>547.0629999999999</v>
       </c>
       <c r="F74">
-        <v>758.2319999999999</v>
+        <v>768.7629999999999</v>
       </c>
       <c r="G74">
         <v>21.7</v>
@@ -7355,37 +7355,37 @@
         <v>62.75</v>
       </c>
       <c r="M74">
-        <v>178.7911056</v>
+        <v>181.2743154</v>
       </c>
       <c r="N74">
-        <v>-116.0411056</v>
+        <v>-118.5243154</v>
       </c>
       <c r="O74">
-        <v>-23.20822112</v>
+        <v>-23.70486308</v>
       </c>
       <c r="P74">
-        <v>-92.83288447999999</v>
+        <v>-94.81945231999998</v>
       </c>
       <c r="Q74">
-        <v>-55.33288447999999</v>
+        <v>-57.31945231999998</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2175095176487159</v>
+        <v>0.2238691294134832</v>
       </c>
       <c r="T74">
-        <v>3.257266099203872</v>
+        <v>3.37790558435957</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.07019364838023577</v>
+        <v>0.06923209155310925</v>
       </c>
       <c r="W74">
-        <v>0.2192483377119404</v>
+        <v>0.2194750728117768</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3509682419011788</v>
+        <v>0.3461604577655463</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2206614680942375</v>
+        <v>0.2225614680942375</v>
       </c>
       <c r="C75">
-        <v>-403.583719736973</v>
+        <v>-417.5596174235386</v>
       </c>
       <c r="D75">
-        <v>343.479280263027</v>
+        <v>340.0343825764613</v>
       </c>
       <c r="E75">
-        <v>547.0629999999999</v>
+        <v>557.5939999999998</v>
       </c>
       <c r="F75">
-        <v>768.7629999999999</v>
+        <v>779.2939999999999</v>
       </c>
       <c r="G75">
         <v>21.7</v>
@@ -7437,37 +7437,37 @@
         <v>62.75</v>
       </c>
       <c r="M75">
-        <v>181.2743154</v>
+        <v>183.7575252</v>
       </c>
       <c r="N75">
-        <v>-118.5243154</v>
+        <v>-121.0075252</v>
       </c>
       <c r="O75">
-        <v>-23.70486308</v>
+        <v>-24.20150504</v>
       </c>
       <c r="P75">
-        <v>-94.81945231999998</v>
+        <v>-96.80602015999997</v>
       </c>
       <c r="Q75">
-        <v>-57.31945231999998</v>
+        <v>-59.30602015999997</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2238691294134832</v>
+        <v>0.2307179420832325</v>
       </c>
       <c r="T75">
-        <v>3.37790558435957</v>
+        <v>3.507825029911862</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.06923209155310925</v>
+        <v>0.06829652274833752</v>
       </c>
       <c r="W75">
-        <v>0.2194750728117768</v>
+        <v>0.219695679935942</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3461604577655463</v>
+        <v>0.3414826137416875</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2225614680942375</v>
+        <v>0.2244614680942376</v>
       </c>
       <c r="C76">
-        <v>-417.5596174235386</v>
+        <v>-431.4671006217222</v>
       </c>
       <c r="D76">
-        <v>340.0343825764613</v>
+        <v>336.6578993782777</v>
       </c>
       <c r="E76">
-        <v>557.5939999999998</v>
+        <v>568.125</v>
       </c>
       <c r="F76">
-        <v>779.2939999999999</v>
+        <v>789.8249999999999</v>
       </c>
       <c r="G76">
         <v>21.7</v>
@@ -7519,37 +7519,37 @@
         <v>62.75</v>
       </c>
       <c r="M76">
-        <v>183.7575252</v>
+        <v>186.240735</v>
       </c>
       <c r="N76">
-        <v>-121.0075252</v>
+        <v>-123.490735</v>
       </c>
       <c r="O76">
-        <v>-24.20150504</v>
+        <v>-24.698147</v>
       </c>
       <c r="P76">
-        <v>-96.80602015999997</v>
+        <v>-98.79258799999999</v>
       </c>
       <c r="Q76">
-        <v>-59.30602015999997</v>
+        <v>-61.29258799999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2307179420832325</v>
+        <v>0.2381146597665618</v>
       </c>
       <c r="T76">
-        <v>3.507825029911862</v>
+        <v>3.648138031108336</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.06829652274833752</v>
+        <v>0.06738590244502633</v>
       </c>
       <c r="W76">
-        <v>0.219695679935942</v>
+        <v>0.2199104042034628</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3414826137416875</v>
+        <v>0.3369295122251317</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2244614680942376</v>
+        <v>0.2263614680942375</v>
       </c>
       <c r="C77">
-        <v>-431.4671006217222</v>
+        <v>-445.3081873256545</v>
       </c>
       <c r="D77">
-        <v>336.6578993782777</v>
+        <v>333.3478126743455</v>
       </c>
       <c r="E77">
-        <v>568.125</v>
+        <v>578.6559999999999</v>
       </c>
       <c r="F77">
-        <v>789.8249999999999</v>
+        <v>800.356</v>
       </c>
       <c r="G77">
         <v>21.7</v>
@@ -7601,37 +7601,37 @@
         <v>62.75</v>
       </c>
       <c r="M77">
-        <v>186.240735</v>
+        <v>188.7239448</v>
       </c>
       <c r="N77">
-        <v>-123.490735</v>
+        <v>-125.9739448</v>
       </c>
       <c r="O77">
-        <v>-24.698147</v>
+        <v>-25.19478896</v>
       </c>
       <c r="P77">
-        <v>-98.79258799999999</v>
+        <v>-100.77915584</v>
       </c>
       <c r="Q77">
-        <v>-61.29258799999999</v>
+        <v>-63.27915584</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2381146597665618</v>
+        <v>0.2461277705901686</v>
       </c>
       <c r="T77">
-        <v>3.648138031108336</v>
+        <v>3.800143782404517</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.06738590244502633</v>
+        <v>0.06649924583390757</v>
       </c>
       <c r="W77">
-        <v>0.2199104042034628</v>
+        <v>0.2201194778323646</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3369295122251317</v>
+        <v>0.3324962291695378</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2263614680942375</v>
+        <v>0.2282614680942376</v>
       </c>
       <c r="C78">
-        <v>-445.3081873256545</v>
+        <v>-459.0848169369421</v>
       </c>
       <c r="D78">
-        <v>333.3478126743455</v>
+        <v>330.1021830630579</v>
       </c>
       <c r="E78">
-        <v>578.6559999999999</v>
+        <v>589.1869999999999</v>
       </c>
       <c r="F78">
-        <v>800.356</v>
+        <v>810.8869999999999</v>
       </c>
       <c r="G78">
         <v>21.7</v>
@@ -7683,37 +7683,37 @@
         <v>62.75</v>
       </c>
       <c r="M78">
-        <v>188.7239448</v>
+        <v>191.2071546</v>
       </c>
       <c r="N78">
-        <v>-125.9739448</v>
+        <v>-128.4571546</v>
       </c>
       <c r="O78">
-        <v>-25.19478896</v>
+        <v>-25.69143092</v>
       </c>
       <c r="P78">
-        <v>-100.77915584</v>
+        <v>-102.76572368</v>
       </c>
       <c r="Q78">
-        <v>-63.27915584</v>
+        <v>-65.26572367999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2461277705901686</v>
+        <v>0.2548376736593064</v>
       </c>
       <c r="T78">
-        <v>3.800143782404517</v>
+        <v>3.965367425117758</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.06649924583390757</v>
+        <v>0.06563561926463604</v>
       </c>
       <c r="W78">
-        <v>0.2201194778323646</v>
+        <v>0.2203231209773988</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3324962291695378</v>
+        <v>0.3281780963231802</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2282614680942376</v>
+        <v>0.2301614680942376</v>
       </c>
       <c r="C79">
-        <v>-459.0848169369421</v>
+        <v>-472.7988540538417</v>
       </c>
       <c r="D79">
-        <v>330.1021830630579</v>
+        <v>326.9191459461583</v>
       </c>
       <c r="E79">
-        <v>589.1869999999999</v>
+        <v>599.7180000000001</v>
       </c>
       <c r="F79">
-        <v>810.8869999999999</v>
+        <v>821.418</v>
       </c>
       <c r="G79">
         <v>21.7</v>
@@ -7765,37 +7765,37 @@
         <v>62.75</v>
       </c>
       <c r="M79">
-        <v>191.2071546</v>
+        <v>193.6903644</v>
       </c>
       <c r="N79">
-        <v>-128.4571546</v>
+        <v>-130.9403644</v>
       </c>
       <c r="O79">
-        <v>-25.69143092</v>
+        <v>-26.18807288000001</v>
       </c>
       <c r="P79">
-        <v>-102.76572368</v>
+        <v>-104.75229152</v>
       </c>
       <c r="Q79">
-        <v>-65.26572367999999</v>
+        <v>-67.25229152000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2548376736593064</v>
+        <v>0.2643393860983658</v>
       </c>
       <c r="T79">
-        <v>3.965367425117758</v>
+        <v>4.145611398986746</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.06563561926463604</v>
+        <v>0.06479413696637147</v>
       </c>
       <c r="W79">
-        <v>0.2203231209773988</v>
+        <v>0.2205215425033296</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3281780963231802</v>
+        <v>0.3239706848318573</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2301614680942376</v>
+        <v>0.2320614680942376</v>
       </c>
       <c r="C80">
-        <v>-472.7988540538417</v>
+        <v>-486.4520920433026</v>
       </c>
       <c r="D80">
-        <v>326.9191459461583</v>
+        <v>323.7969079566973</v>
       </c>
       <c r="E80">
-        <v>599.7180000000001</v>
+        <v>610.249</v>
       </c>
       <c r="F80">
-        <v>821.418</v>
+        <v>831.949</v>
       </c>
       <c r="G80">
         <v>21.7</v>
@@ -7847,37 +7847,37 @@
         <v>62.75</v>
       </c>
       <c r="M80">
-        <v>193.6903644</v>
+        <v>196.1735742</v>
       </c>
       <c r="N80">
-        <v>-130.9403644</v>
+        <v>-133.4235742</v>
       </c>
       <c r="O80">
-        <v>-26.18807288000001</v>
+        <v>-26.68471484</v>
       </c>
       <c r="P80">
-        <v>-104.75229152</v>
+        <v>-106.73885936</v>
       </c>
       <c r="Q80">
-        <v>-67.25229152000001</v>
+        <v>-69.23885935999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2643393860983658</v>
+        <v>0.2747460235316213</v>
       </c>
       <c r="T80">
-        <v>4.145611398986746</v>
+        <v>4.343021465605164</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.06479413696637147</v>
+        <v>0.06397395801743005</v>
       </c>
       <c r="W80">
-        <v>0.2205215425033296</v>
+        <v>0.22071494069949</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3239706848318573</v>
+        <v>0.3198697900871503</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2320614680942376</v>
+        <v>0.2339614680942376</v>
       </c>
       <c r="C81">
-        <v>-486.4520920433026</v>
+        <v>-500.0462564102586</v>
       </c>
       <c r="D81">
-        <v>323.7969079566973</v>
+        <v>320.7337435897414</v>
       </c>
       <c r="E81">
-        <v>610.249</v>
+        <v>620.78</v>
       </c>
       <c r="F81">
-        <v>831.949</v>
+        <v>842.48</v>
       </c>
       <c r="G81">
         <v>21.7</v>
@@ -7929,37 +7929,37 @@
         <v>62.75</v>
       </c>
       <c r="M81">
-        <v>196.1735742</v>
+        <v>198.656784</v>
       </c>
       <c r="N81">
-        <v>-133.4235742</v>
+        <v>-135.906784</v>
       </c>
       <c r="O81">
-        <v>-26.68471484</v>
+        <v>-27.1813568</v>
       </c>
       <c r="P81">
-        <v>-106.73885936</v>
+        <v>-108.7254272</v>
       </c>
       <c r="Q81">
-        <v>-69.23885935999999</v>
+        <v>-71.22542720000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2747460235316213</v>
+        <v>0.2861933247082023</v>
       </c>
       <c r="T81">
-        <v>4.343021465605164</v>
+        <v>4.560172538885421</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.06397395801743005</v>
+        <v>0.06317428354221218</v>
       </c>
       <c r="W81">
-        <v>0.22071494069949</v>
+        <v>0.2209035039407464</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3198697900871503</v>
+        <v>0.3158714177110609</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2339614680942376</v>
+        <v>0.2358614680942376</v>
       </c>
       <c r="C82">
-        <v>-500.0462564102586</v>
+        <v>-513.5830079774663</v>
       </c>
       <c r="D82">
-        <v>320.7337435897414</v>
+        <v>317.7279920225337</v>
       </c>
       <c r="E82">
-        <v>620.78</v>
+        <v>631.3109999999999</v>
       </c>
       <c r="F82">
-        <v>842.48</v>
+        <v>853.011</v>
       </c>
       <c r="G82">
         <v>21.7</v>
@@ -8011,37 +8011,37 @@
         <v>62.75</v>
       </c>
       <c r="M82">
-        <v>198.656784</v>
+        <v>201.1399938</v>
       </c>
       <c r="N82">
-        <v>-135.906784</v>
+        <v>-138.3899938</v>
       </c>
       <c r="O82">
-        <v>-27.1813568</v>
+        <v>-27.67799876</v>
       </c>
       <c r="P82">
-        <v>-108.7254272</v>
+        <v>-110.71199504</v>
       </c>
       <c r="Q82">
-        <v>-71.22542720000001</v>
+        <v>-73.21199504000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2861933247082023</v>
+        <v>0.2988456049560025</v>
       </c>
       <c r="T82">
-        <v>4.560172538885421</v>
+        <v>4.800181619879392</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.06317428354221218</v>
+        <v>0.06239435411576512</v>
       </c>
       <c r="W82">
-        <v>0.2209035039407464</v>
+        <v>0.2210874112995026</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.3158714177110609</v>
+        <v>0.3119717705788255</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2358614680942376</v>
+        <v>0.2377614680942376</v>
       </c>
       <c r="C83">
-        <v>-513.5830079774663</v>
+        <v>-527.0639458882069</v>
       </c>
       <c r="D83">
-        <v>317.7279920225337</v>
+        <v>314.7780541117932</v>
       </c>
       <c r="E83">
-        <v>631.3109999999999</v>
+        <v>641.8420000000001</v>
       </c>
       <c r="F83">
-        <v>853.011</v>
+        <v>863.542</v>
       </c>
       <c r="G83">
         <v>21.7</v>
@@ -8093,37 +8093,37 @@
         <v>62.75</v>
       </c>
       <c r="M83">
-        <v>201.1399938</v>
+        <v>203.6232036</v>
       </c>
       <c r="N83">
-        <v>-138.3899938</v>
+        <v>-140.8732036</v>
       </c>
       <c r="O83">
-        <v>-27.67799876</v>
+        <v>-28.17464072</v>
       </c>
       <c r="P83">
-        <v>-110.71199504</v>
+        <v>-112.69856288</v>
       </c>
       <c r="Q83">
-        <v>-73.21199504000001</v>
+        <v>-75.19856288000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2988456049560025</v>
+        <v>0.3129036941202248</v>
       </c>
       <c r="T83">
-        <v>4.800181619879392</v>
+        <v>5.066858376539357</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.06239435411576512</v>
+        <v>0.06163344735825578</v>
       </c>
       <c r="W83">
-        <v>0.2210874112995026</v>
+        <v>0.2212668331129233</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3119717705788255</v>
+        <v>0.3081672367912789</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2377614680942376</v>
+        <v>0.2396614680942376</v>
       </c>
       <c r="C84">
-        <v>-527.0639458882069</v>
+        <v>-540.4906104432534</v>
       </c>
       <c r="D84">
-        <v>314.7780541117932</v>
+        <v>311.8823895567465</v>
       </c>
       <c r="E84">
-        <v>641.8420000000001</v>
+        <v>652.373</v>
       </c>
       <c r="F84">
-        <v>863.542</v>
+        <v>874.073</v>
       </c>
       <c r="G84">
         <v>21.7</v>
@@ -8175,37 +8175,37 @@
         <v>62.75</v>
       </c>
       <c r="M84">
-        <v>203.6232036</v>
+        <v>206.1064134</v>
       </c>
       <c r="N84">
-        <v>-140.8732036</v>
+        <v>-143.3564134</v>
       </c>
       <c r="O84">
-        <v>-28.17464072</v>
+        <v>-28.67128268</v>
       </c>
       <c r="P84">
-        <v>-112.69856288</v>
+        <v>-114.68513072</v>
       </c>
       <c r="Q84">
-        <v>-75.19856288000001</v>
+        <v>-77.18513072</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3129036941202248</v>
+        <v>0.3286156761272969</v>
       </c>
       <c r="T84">
-        <v>5.066858376539357</v>
+        <v>5.364908869276967</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.06163344735825578</v>
+        <v>0.06089087570333705</v>
       </c>
       <c r="W84">
-        <v>0.2212668331129233</v>
+        <v>0.2214419315091531</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3081672367912789</v>
+        <v>0.3044543785166852</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2396614680942376</v>
+        <v>0.2415614680942376</v>
       </c>
       <c r="C85">
-        <v>-540.4906104432534</v>
+        <v>-553.8644857826828</v>
       </c>
       <c r="D85">
-        <v>311.8823895567465</v>
+        <v>309.0395142173173</v>
       </c>
       <c r="E85">
-        <v>652.373</v>
+        <v>662.904</v>
       </c>
       <c r="F85">
-        <v>874.073</v>
+        <v>884.604</v>
       </c>
       <c r="G85">
         <v>21.7</v>
@@ -8257,37 +8257,37 @@
         <v>62.75</v>
       </c>
       <c r="M85">
-        <v>206.1064134</v>
+        <v>208.5896232</v>
       </c>
       <c r="N85">
-        <v>-143.3564134</v>
+        <v>-145.8396232</v>
       </c>
       <c r="O85">
-        <v>-28.67128268</v>
+        <v>-29.16792464</v>
       </c>
       <c r="P85">
-        <v>-114.68513072</v>
+        <v>-116.67169856</v>
       </c>
       <c r="Q85">
-        <v>-77.18513072</v>
+        <v>-79.17169856000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3286156761272969</v>
+        <v>0.3462916558852531</v>
       </c>
       <c r="T85">
-        <v>5.364908869276967</v>
+        <v>5.700215673606779</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.06089087570333705</v>
+        <v>0.06016598432591636</v>
       </c>
       <c r="W85">
-        <v>0.2214419315091531</v>
+        <v>0.2216128608959489</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3044543785166852</v>
+        <v>0.3008299216295818</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2415614680942376</v>
+        <v>0.2434614680942375</v>
       </c>
       <c r="C86">
-        <v>-553.8644857826827</v>
+        <v>-567.187002422338</v>
       </c>
       <c r="D86">
-        <v>309.0395142173173</v>
+        <v>306.2479975776619</v>
       </c>
       <c r="E86">
-        <v>662.904</v>
+        <v>673.4349999999999</v>
       </c>
       <c r="F86">
-        <v>884.6039999999999</v>
+        <v>895.1349999999999</v>
       </c>
       <c r="G86">
         <v>21.7</v>
@@ -8339,37 +8339,37 @@
         <v>62.75</v>
       </c>
       <c r="M86">
-        <v>208.5896232</v>
+        <v>211.072833</v>
       </c>
       <c r="N86">
-        <v>-145.8396232</v>
+        <v>-148.322833</v>
       </c>
       <c r="O86">
-        <v>-29.16792464</v>
+        <v>-29.6645666</v>
       </c>
       <c r="P86">
-        <v>-116.67169856</v>
+        <v>-118.6582664</v>
       </c>
       <c r="Q86">
-        <v>-79.17169856000001</v>
+        <v>-81.15826639999997</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3462916558852528</v>
+        <v>0.3663244329442697</v>
       </c>
       <c r="T86">
-        <v>5.700215673606775</v>
+        <v>6.080230051847226</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.06016598432591636</v>
+        <v>0.05945814921619971</v>
       </c>
       <c r="W86">
-        <v>0.2216128608959489</v>
+        <v>0.2217797684148201</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3008299216295818</v>
+        <v>0.2972907460809985</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2434614680942375</v>
+        <v>0.2453614680942375</v>
       </c>
       <c r="C87">
-        <v>-567.187002422338</v>
+        <v>-580.4595396540552</v>
       </c>
       <c r="D87">
-        <v>306.2479975776619</v>
+        <v>303.5064603459447</v>
       </c>
       <c r="E87">
-        <v>673.4349999999999</v>
+        <v>683.9659999999999</v>
       </c>
       <c r="F87">
-        <v>895.1349999999999</v>
+        <v>905.6659999999999</v>
       </c>
       <c r="G87">
         <v>21.7</v>
@@ -8421,37 +8421,37 @@
         <v>62.75</v>
       </c>
       <c r="M87">
-        <v>211.072833</v>
+        <v>213.5560428</v>
       </c>
       <c r="N87">
-        <v>-148.322833</v>
+        <v>-150.8060428</v>
       </c>
       <c r="O87">
-        <v>-29.6645666</v>
+        <v>-30.16120856</v>
       </c>
       <c r="P87">
-        <v>-118.6582664</v>
+        <v>-120.64483424</v>
       </c>
       <c r="Q87">
-        <v>-81.15826639999997</v>
+        <v>-83.14483423999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3663244329442697</v>
+        <v>0.3892190352974318</v>
       </c>
       <c r="T87">
-        <v>6.080230051847226</v>
+        <v>6.514532198407744</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.05945814921619971</v>
+        <v>0.05876677538810435</v>
       </c>
       <c r="W87">
-        <v>0.2217797684148201</v>
+        <v>0.221942794363485</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2972907460809985</v>
+        <v>0.2938338769405218</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2453614680942375</v>
+        <v>0.2472614680942376</v>
       </c>
       <c r="C88">
-        <v>-580.4595396540552</v>
+        <v>-593.6834278181104</v>
       </c>
       <c r="D88">
-        <v>303.5064603459447</v>
+        <v>300.8135721818894</v>
       </c>
       <c r="E88">
-        <v>683.9659999999999</v>
+        <v>694.4969999999998</v>
       </c>
       <c r="F88">
-        <v>905.6659999999999</v>
+        <v>916.1969999999999</v>
       </c>
       <c r="G88">
         <v>21.7</v>
@@ -8503,37 +8503,37 @@
         <v>62.75</v>
       </c>
       <c r="M88">
-        <v>213.5560428</v>
+        <v>216.0392526</v>
       </c>
       <c r="N88">
-        <v>-150.8060428</v>
+        <v>-153.2892526</v>
       </c>
       <c r="O88">
-        <v>-30.16120856</v>
+        <v>-30.65785052</v>
       </c>
       <c r="P88">
-        <v>-120.64483424</v>
+        <v>-122.63140208</v>
       </c>
       <c r="Q88">
-        <v>-83.14483423999999</v>
+        <v>-85.13140207999997</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3892190352974318</v>
+        <v>0.4156358841664651</v>
       </c>
       <c r="T88">
-        <v>6.514532198407744</v>
+        <v>7.015650059823724</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.05876677538810435</v>
+        <v>0.0580912952112296</v>
       </c>
       <c r="W88">
-        <v>0.221942794363485</v>
+        <v>0.2221020725891921</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2938338769405218</v>
+        <v>0.290456476056148</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2472614680942376</v>
+        <v>0.2491614680942375</v>
       </c>
       <c r="C89">
-        <v>-593.6834278181104</v>
+        <v>-606.8599504557569</v>
       </c>
       <c r="D89">
-        <v>300.8135721818894</v>
+        <v>298.168049544243</v>
       </c>
       <c r="E89">
-        <v>694.4969999999998</v>
+        <v>705.028</v>
       </c>
       <c r="F89">
-        <v>916.1969999999999</v>
+        <v>926.728</v>
       </c>
       <c r="G89">
         <v>21.7</v>
@@ -8585,37 +8585,37 @@
         <v>62.75</v>
       </c>
       <c r="M89">
-        <v>216.0392526</v>
+        <v>218.5224624</v>
       </c>
       <c r="N89">
-        <v>-153.2892526</v>
+        <v>-155.7724624</v>
       </c>
       <c r="O89">
-        <v>-30.65785052</v>
+        <v>-31.15449248</v>
       </c>
       <c r="P89">
-        <v>-122.63140208</v>
+        <v>-124.61796992</v>
       </c>
       <c r="Q89">
-        <v>-85.13140207999997</v>
+        <v>-87.11796991999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4156358841664651</v>
+        <v>0.4464555411803371</v>
       </c>
       <c r="T89">
-        <v>7.015650059823724</v>
+        <v>7.600287564809034</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.0580912952112296</v>
+        <v>0.05743116685655653</v>
       </c>
       <c r="W89">
-        <v>0.2221020725891921</v>
+        <v>0.222257730855224</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.290456476056148</v>
+        <v>0.2871558342827827</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2491614680942375</v>
+        <v>0.2510614680942376</v>
       </c>
       <c r="C90">
-        <v>-606.8599504557569</v>
+        <v>-619.9903463491681</v>
       </c>
       <c r="D90">
-        <v>298.168049544243</v>
+        <v>295.5686536508318</v>
       </c>
       <c r="E90">
-        <v>705.028</v>
+        <v>715.559</v>
       </c>
       <c r="F90">
-        <v>926.728</v>
+        <v>937.2589999999999</v>
       </c>
       <c r="G90">
         <v>21.7</v>
@@ -8667,37 +8667,37 @@
         <v>62.75</v>
       </c>
       <c r="M90">
-        <v>218.5224624</v>
+        <v>221.0056722</v>
       </c>
       <c r="N90">
-        <v>-155.7724624</v>
+        <v>-158.2556722</v>
       </c>
       <c r="O90">
-        <v>-31.15449248</v>
+        <v>-31.65113444</v>
       </c>
       <c r="P90">
-        <v>-124.61796992</v>
+        <v>-126.60453776</v>
       </c>
       <c r="Q90">
-        <v>-87.11796991999999</v>
+        <v>-89.10453776</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4464555411803371</v>
+        <v>0.4828787721967315</v>
       </c>
       <c r="T90">
-        <v>7.600287564809034</v>
+        <v>8.291222797973493</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.05743116685655653</v>
+        <v>0.0567858728469323</v>
       </c>
       <c r="W90">
-        <v>0.222257730855224</v>
+        <v>0.2224098911826934</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2871558342827827</v>
+        <v>0.2839293642346615</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2510614680942376</v>
+        <v>0.2529614680942376</v>
       </c>
       <c r="C91">
-        <v>-619.9903463491681</v>
+        <v>-633.0758114555998</v>
       </c>
       <c r="D91">
-        <v>295.5686536508318</v>
+        <v>293.0141885444002</v>
       </c>
       <c r="E91">
-        <v>715.559</v>
+        <v>726.0899999999999</v>
       </c>
       <c r="F91">
-        <v>937.2589999999999</v>
+        <v>947.79</v>
       </c>
       <c r="G91">
         <v>21.7</v>
@@ -8749,37 +8749,37 @@
         <v>62.75</v>
       </c>
       <c r="M91">
-        <v>221.0056722</v>
+        <v>223.488882</v>
       </c>
       <c r="N91">
-        <v>-158.2556722</v>
+        <v>-160.738882</v>
       </c>
       <c r="O91">
-        <v>-31.65113444</v>
+        <v>-32.1477764</v>
       </c>
       <c r="P91">
-        <v>-126.60453776</v>
+        <v>-128.5911056</v>
       </c>
       <c r="Q91">
-        <v>-89.10453776</v>
+        <v>-91.09110559999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4828787721967315</v>
+        <v>0.5265866494164047</v>
       </c>
       <c r="T91">
-        <v>8.291222797973493</v>
+        <v>9.120345077770843</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.0567858728469323</v>
+        <v>0.05615491870418861</v>
       </c>
       <c r="W91">
-        <v>0.2224098911826934</v>
+        <v>0.2225586701695523</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2839293642346615</v>
+        <v>0.280774593520943</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2529614680942376</v>
+        <v>0.2548614680942376</v>
       </c>
       <c r="C92">
-        <v>-633.0758114555998</v>
+        <v>-646.1175007421139</v>
       </c>
       <c r="D92">
-        <v>293.0141885444002</v>
+        <v>290.503499257886</v>
       </c>
       <c r="E92">
-        <v>726.0899999999999</v>
+        <v>736.6209999999999</v>
       </c>
       <c r="F92">
-        <v>947.79</v>
+        <v>958.3209999999999</v>
       </c>
       <c r="G92">
         <v>21.7</v>
@@ -8831,37 +8831,37 @@
         <v>62.75</v>
       </c>
       <c r="M92">
-        <v>223.488882</v>
+        <v>225.9720918</v>
       </c>
       <c r="N92">
-        <v>-160.738882</v>
+        <v>-163.2220918</v>
       </c>
       <c r="O92">
-        <v>-32.1477764</v>
+        <v>-32.64441836</v>
       </c>
       <c r="P92">
-        <v>-128.5911056</v>
+        <v>-130.57767344</v>
       </c>
       <c r="Q92">
-        <v>-91.09110559999999</v>
+        <v>-93.07767343999998</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5265866494164047</v>
+        <v>0.5800073882404496</v>
       </c>
       <c r="T92">
-        <v>9.120345077770843</v>
+        <v>10.13371675307872</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.05615491870418861</v>
+        <v>0.05553783168546126</v>
       </c>
       <c r="W92">
-        <v>0.2225586701695523</v>
+        <v>0.2227041792885683</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.280774593520943</v>
+        <v>0.2776891584273063</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2548614680942376</v>
+        <v>0.2567614680942376</v>
       </c>
       <c r="C93">
-        <v>-646.1175007421139</v>
+        <v>-659.1165299267802</v>
       </c>
       <c r="D93">
-        <v>290.503499257886</v>
+        <v>288.0354700732198</v>
       </c>
       <c r="E93">
-        <v>736.6209999999999</v>
+        <v>747.152</v>
       </c>
       <c r="F93">
-        <v>958.3209999999999</v>
+        <v>968.852</v>
       </c>
       <c r="G93">
         <v>21.7</v>
@@ -8913,37 +8913,37 @@
         <v>62.75</v>
       </c>
       <c r="M93">
-        <v>225.9720918</v>
+        <v>228.4553016</v>
       </c>
       <c r="N93">
-        <v>-163.2220918</v>
+        <v>-165.7053016</v>
       </c>
       <c r="O93">
-        <v>-32.64441836</v>
+        <v>-33.14106032</v>
       </c>
       <c r="P93">
-        <v>-130.57767344</v>
+        <v>-132.56424128</v>
       </c>
       <c r="Q93">
-        <v>-93.07767343999998</v>
+        <v>-95.06424128</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5800073882404496</v>
+        <v>0.6467833117705061</v>
       </c>
       <c r="T93">
-        <v>10.13371675307872</v>
+        <v>11.40043134721356</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.05553783168546126</v>
+        <v>0.05493415960192363</v>
       </c>
       <c r="W93">
-        <v>0.2227041792885683</v>
+        <v>0.2228465251658664</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2776891584273063</v>
+        <v>0.2746707980096181</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2567614680942376</v>
+        <v>0.2586614680942376</v>
       </c>
       <c r="C94">
-        <v>-659.1165299267802</v>
+        <v>-672.0739771318681</v>
       </c>
       <c r="D94">
-        <v>288.0354700732198</v>
+        <v>285.6090228681319</v>
       </c>
       <c r="E94">
-        <v>747.152</v>
+        <v>757.683</v>
       </c>
       <c r="F94">
-        <v>968.852</v>
+        <v>979.3829999999999</v>
       </c>
       <c r="G94">
         <v>21.7</v>
@@ -8995,37 +8995,37 @@
         <v>62.75</v>
       </c>
       <c r="M94">
-        <v>228.4553016</v>
+        <v>230.9385114</v>
       </c>
       <c r="N94">
-        <v>-165.7053016</v>
+        <v>-168.1885114</v>
       </c>
       <c r="O94">
-        <v>-33.14106032</v>
+        <v>-33.63770228</v>
       </c>
       <c r="P94">
-        <v>-132.56424128</v>
+        <v>-134.55080912</v>
       </c>
       <c r="Q94">
-        <v>-95.06424128</v>
+        <v>-97.05080912</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6467833117705061</v>
+        <v>0.732638070594864</v>
       </c>
       <c r="T94">
-        <v>11.40043134721356</v>
+        <v>13.02906439681549</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.05493415960192363</v>
+        <v>0.05434346971373091</v>
       </c>
       <c r="W94">
-        <v>0.2228465251658664</v>
+        <v>0.2229858098415023</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2746707980096181</v>
+        <v>0.2717173485686546</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2586614680942376</v>
+        <v>0.2605614680942376</v>
       </c>
       <c r="C95">
-        <v>-672.0739771318681</v>
+        <v>-684.9908844541773</v>
       </c>
       <c r="D95">
-        <v>285.6090228681319</v>
+        <v>283.2231155458227</v>
       </c>
       <c r="E95">
-        <v>757.683</v>
+        <v>768.2139999999999</v>
       </c>
       <c r="F95">
-        <v>979.3829999999999</v>
+        <v>989.914</v>
       </c>
       <c r="G95">
         <v>21.7</v>
@@ -9077,37 +9077,37 @@
         <v>62.75</v>
       </c>
       <c r="M95">
-        <v>230.9385114</v>
+        <v>233.4217212</v>
       </c>
       <c r="N95">
-        <v>-168.1885114</v>
+        <v>-170.6717212</v>
       </c>
       <c r="O95">
-        <v>-33.63770228</v>
+        <v>-34.13434424</v>
       </c>
       <c r="P95">
-        <v>-134.55080912</v>
+        <v>-136.53737696</v>
       </c>
       <c r="Q95">
-        <v>-97.05080912</v>
+        <v>-99.03737696000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.732638070594864</v>
+        <v>0.8471110823606751</v>
       </c>
       <c r="T95">
-        <v>13.02906439681549</v>
+        <v>15.20057512961808</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.05434346971373091</v>
+        <v>0.05376534769549973</v>
       </c>
       <c r="W95">
-        <v>0.2229858098415023</v>
+        <v>0.2231221310134012</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2717173485686546</v>
+        <v>0.2688267384774986</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2605614680942376</v>
+        <v>0.2624614680942375</v>
       </c>
       <c r="C96">
-        <v>-684.9908844541773</v>
+        <v>-697.8682594573106</v>
       </c>
       <c r="D96">
-        <v>283.2231155458227</v>
+        <v>280.8767405426894</v>
       </c>
       <c r="E96">
-        <v>768.2139999999999</v>
+        <v>778.7449999999999</v>
       </c>
       <c r="F96">
-        <v>989.914</v>
+        <v>1000.445</v>
       </c>
       <c r="G96">
         <v>21.7</v>
@@ -9159,37 +9159,37 @@
         <v>62.75</v>
       </c>
       <c r="M96">
-        <v>233.4217212</v>
+        <v>235.904931</v>
       </c>
       <c r="N96">
-        <v>-170.6717212</v>
+        <v>-173.154931</v>
       </c>
       <c r="O96">
-        <v>-34.13434424</v>
+        <v>-34.6309862</v>
       </c>
       <c r="P96">
-        <v>-136.53737696</v>
+        <v>-138.5239448</v>
       </c>
       <c r="Q96">
-        <v>-99.03737696000002</v>
+        <v>-101.0239448</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8471110823606751</v>
+        <v>1.007373298832811</v>
       </c>
       <c r="T96">
-        <v>15.20057512961808</v>
+        <v>18.24069015554171</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.05376534769549973</v>
+        <v>0.05319939666712604</v>
       </c>
       <c r="W96">
-        <v>0.2231221310134012</v>
+        <v>0.2232555822658917</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2688267384774986</v>
+        <v>0.2659969833356303</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2624614680942375</v>
+        <v>0.2643614680942376</v>
       </c>
       <c r="C97">
-        <v>-697.8682594573106</v>
+        <v>-710.7070765903808</v>
       </c>
       <c r="D97">
-        <v>280.8767405426894</v>
+        <v>278.5689234096192</v>
       </c>
       <c r="E97">
-        <v>778.7449999999999</v>
+        <v>789.2760000000001</v>
       </c>
       <c r="F97">
-        <v>1000.445</v>
+        <v>1010.976</v>
       </c>
       <c r="G97">
         <v>21.7</v>
@@ -9241,37 +9241,37 @@
         <v>62.75</v>
       </c>
       <c r="M97">
-        <v>235.904931</v>
+        <v>238.3881408</v>
       </c>
       <c r="N97">
-        <v>-173.154931</v>
+        <v>-175.6381408</v>
       </c>
       <c r="O97">
-        <v>-34.6309862</v>
+        <v>-35.12762816</v>
       </c>
       <c r="P97">
-        <v>-138.5239448</v>
+        <v>-140.51051264</v>
       </c>
       <c r="Q97">
-        <v>-101.0239448</v>
+        <v>-103.01051264</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.007373298832811</v>
+        <v>1.247766623541014</v>
       </c>
       <c r="T97">
-        <v>18.24069015554171</v>
+        <v>22.80086269442715</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.05319939666712604</v>
+        <v>0.05264523628517682</v>
       </c>
       <c r="W97">
-        <v>0.2232555822658917</v>
+        <v>0.2233862532839553</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2659969833356303</v>
+        <v>0.2632261814258841</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2643614680942376</v>
+        <v>0.2662614680942376</v>
       </c>
       <c r="C98">
-        <v>-710.7070765903806</v>
+        <v>-723.5082785373443</v>
       </c>
       <c r="D98">
-        <v>278.5689234096193</v>
+        <v>276.2987214626556</v>
       </c>
       <c r="E98">
-        <v>789.2759999999998</v>
+        <v>799.8069999999998</v>
       </c>
       <c r="F98">
-        <v>1010.976</v>
+        <v>1021.507</v>
       </c>
       <c r="G98">
         <v>21.7</v>
@@ -9323,37 +9323,37 @@
         <v>62.75</v>
       </c>
       <c r="M98">
-        <v>238.3881408</v>
+        <v>240.8713506</v>
       </c>
       <c r="N98">
-        <v>-175.6381408</v>
+        <v>-178.1213506</v>
       </c>
       <c r="O98">
-        <v>-35.12762815999999</v>
+        <v>-35.62427012</v>
       </c>
       <c r="P98">
-        <v>-140.51051264</v>
+        <v>-142.49708048</v>
       </c>
       <c r="Q98">
-        <v>-103.01051264</v>
+        <v>-104.99708048</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.24776662354101</v>
+        <v>1.648422164721347</v>
       </c>
       <c r="T98">
-        <v>22.80086269442708</v>
+        <v>30.40115025923611</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.05264523628517682</v>
+        <v>0.05210250189048428</v>
       </c>
       <c r="W98">
-        <v>0.2233862532839553</v>
+        <v>0.2235142300542238</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2632261814258842</v>
+        <v>0.2605125094524214</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2662614680942376</v>
+        <v>0.2681614680942376</v>
       </c>
       <c r="C99">
-        <v>-723.5082785373443</v>
+        <v>-736.2727775008939</v>
       </c>
       <c r="D99">
-        <v>276.2987214626556</v>
+        <v>274.0652224991059</v>
       </c>
       <c r="E99">
-        <v>799.8069999999998</v>
+        <v>810.3379999999997</v>
       </c>
       <c r="F99">
-        <v>1021.507</v>
+        <v>1032.038</v>
       </c>
       <c r="G99">
         <v>21.7</v>
@@ -9405,37 +9405,37 @@
         <v>62.75</v>
       </c>
       <c r="M99">
-        <v>240.8713506</v>
+        <v>243.3545604</v>
       </c>
       <c r="N99">
-        <v>-178.1213506</v>
+        <v>-180.6045604</v>
       </c>
       <c r="O99">
-        <v>-35.62427012</v>
+        <v>-36.12091208</v>
       </c>
       <c r="P99">
-        <v>-142.49708048</v>
+        <v>-144.48364832</v>
       </c>
       <c r="Q99">
-        <v>-104.99708048</v>
+        <v>-106.98364832</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.648422164721347</v>
+        <v>2.44973324708202</v>
       </c>
       <c r="T99">
-        <v>30.40115025923611</v>
+        <v>45.60172538885416</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.05210250189048428</v>
+        <v>0.05157084370792832</v>
       </c>
       <c r="W99">
-        <v>0.2235142300542238</v>
+        <v>0.2236395950536705</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2605125094524214</v>
+        <v>0.2578542185396416</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2681614680942376</v>
+        <v>0.2700614680942375</v>
       </c>
       <c r="C100">
-        <v>-736.2727775008939</v>
+        <v>-749.0014564245751</v>
       </c>
       <c r="D100">
-        <v>274.0652224991059</v>
+        <v>271.8675435754249</v>
       </c>
       <c r="E100">
-        <v>810.3379999999997</v>
+        <v>820.8689999999999</v>
       </c>
       <c r="F100">
-        <v>1032.038</v>
+        <v>1042.569</v>
       </c>
       <c r="G100">
         <v>21.7</v>
@@ -9487,37 +9487,37 @@
         <v>62.75</v>
       </c>
       <c r="M100">
-        <v>243.3545604</v>
+        <v>245.8377702</v>
       </c>
       <c r="N100">
-        <v>-180.6045604</v>
+        <v>-183.0877702</v>
       </c>
       <c r="O100">
-        <v>-36.12091208</v>
+        <v>-36.61755404</v>
       </c>
       <c r="P100">
-        <v>-144.48364832</v>
+        <v>-146.47021616</v>
       </c>
       <c r="Q100">
-        <v>-106.98364832</v>
+        <v>-108.97021616</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.44973324708202</v>
+        <v>4.853666494164041</v>
       </c>
       <c r="T100">
-        <v>45.60172538885416</v>
+        <v>91.20345077770833</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.05157084370792832</v>
+        <v>0.05104992609471692</v>
       </c>
       <c r="W100">
-        <v>0.2236395950536705</v>
+        <v>0.2237624274268658</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2578542185396416</v>
+        <v>0.2552496304735846</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2700614680942375</v>
-      </c>
-      <c r="C101">
-        <v>-749.0014564245751</v>
-      </c>
-      <c r="D101">
-        <v>271.8675435754249</v>
-      </c>
-      <c r="E101">
-        <v>820.8689999999999</v>
-      </c>
-      <c r="F101">
-        <v>1042.569</v>
-      </c>
-      <c r="G101">
-        <v>21.7</v>
-      </c>
-      <c r="H101">
-        <v>831.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>100.25</v>
-      </c>
-      <c r="K101">
-        <v>37.5</v>
-      </c>
-      <c r="L101">
-        <v>62.75</v>
-      </c>
-      <c r="M101">
-        <v>245.8377702</v>
-      </c>
-      <c r="N101">
-        <v>-183.0877702</v>
-      </c>
-      <c r="O101">
-        <v>-36.61755404</v>
-      </c>
-      <c r="P101">
-        <v>-146.47021616</v>
-      </c>
-      <c r="Q101">
-        <v>-108.97021616</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.853666494164041</v>
-      </c>
-      <c r="T101">
-        <v>91.20345077770833</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.05104992609471692</v>
-      </c>
-      <c r="W101">
-        <v>0.2237624274268658</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2552496304735846</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
